--- a/1.xlsx
+++ b/1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>to_address</t>
   </si>
@@ -40,18 +40,21 @@
     <t>celestia1pa56a9fg5jhxrduru275vn2y7fpkxmx6up9jhw</t>
   </si>
   <si>
+    <t>celestia1p7pucfsptdz7mpy32udr52v04edfqrqr86vzj3</t>
+  </si>
+  <si>
     <t>celestia1zvn0400rgpyhvrse936p25mfkrnnr8elkjdzzt</t>
   </si>
   <si>
-    <t>celestia1zwtv7pplzh7m3t4m2zel8c0q78qsyptvqpjctt</t>
-  </si>
-  <si>
     <t>celestia1z3wu5uh60kmczccpxxlk469ue4muh63h8d9xte</t>
   </si>
   <si>
     <t>celestia1zmruurfzccvmdgcuw2rv5rla6etk36k62a6w3m</t>
   </si>
   <si>
+    <t>celestia1rzpz4fqmrcxkvdnskmx2k9wdqxv5ne3q4n3ue3</t>
+  </si>
+  <si>
     <t>celestia1r3sglnjc34q2l0nf2rl2dh6slum564mmk5249m</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>celestia1yyvdwarlwt4sz6qslzs5sx5jlzu6guaj783tlx</t>
   </si>
   <si>
+    <t>celestia1ysthp74n2wxt4flmzyxrhza8rvxzr9mcqr58re</t>
+  </si>
+  <si>
     <t>celestia1ymwgg85shgthy4gsp7qf59jpf0pz4c3rz3aqqm</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>celestia1xzq3z62dvsrlkpmsw8ju4unh95sr7svz8s7rjd</t>
   </si>
   <si>
+    <t>celestia1x3xqdgpcc075wpr2h6zpcywewjl8pjl64n4h32</t>
+  </si>
+  <si>
     <t>celestia1xkhs27xj8tjd74lyfhcgw4g03krnpn9wqz6mh7</t>
   </si>
   <si>
@@ -91,33 +100,60 @@
     <t>celestia184mdhx7jq5al582e6t3ssdev08ccghk5lm6awh</t>
   </si>
   <si>
+    <t>celestia18kvjxrrp935gss49xpuqkn285m64zs9vdtz7lw</t>
+  </si>
+  <si>
     <t>celestia1gfs3scxqhne0jg5eft55cplj4rlwfu458s7jc3</t>
   </si>
   <si>
+    <t>celestia1gsagmc8wxyzcz3c0nn8zv2kggpcnywynrehuk7</t>
+  </si>
+  <si>
     <t>celestia12sxx3f0knswnxh763kpddwaygt8qfy0jke96gl</t>
   </si>
   <si>
+    <t>celestia12erey3cnxl700ggcrfdmu2llhmjwn0f99v3wpv</t>
+  </si>
+  <si>
+    <t>celestia1ty53xnrqsmk9zupyjgxktpt2gtyshvu45n0rq0</t>
+  </si>
+  <si>
     <t>celestia1tgyqvzknt3l0qv6p98guu859mv8htpz6nmqvz0</t>
   </si>
   <si>
+    <t>celestia1tjuf68dfhymtc3j3zlu9d7m6vjeqrcmp76uqqr</t>
+  </si>
+  <si>
+    <t>celestia1vj6vnd7mdntguhs7j2fu3vjzt4v7u6xvqa389e</t>
+  </si>
+  <si>
     <t>celestia1vkngvnelw4tgahyn20sr0kvk9jq8wrfekx6ank</t>
   </si>
   <si>
     <t>celestia1dqtfsays94pktsj2dachaju37v2jxpjsgz2acz</t>
   </si>
   <si>
+    <t>celestia1de88sp2h3955ktrjgnm0jkhy8dttsgdzye3xus</t>
+  </si>
+  <si>
     <t>celestia1duls39pg7uqze7vpz65n22re72nycvmrgkg4kr</t>
   </si>
   <si>
+    <t>celestia1wqjagmsh5tyv4eztpypqgklyq23aepxf3q5nex</t>
+  </si>
+  <si>
+    <t>celestia1wxv8jnx4tnr5rr5uwnx05g3s74tcpzajssfsav</t>
+  </si>
+  <si>
+    <t>celestia1wxhgzdwmek4duaevg2zwzguev8tnm4ncjrhau5</t>
+  </si>
+  <si>
     <t>celestia1wgdegtthkx0n5fmyt2l2xn9jchywffac8q9eea</t>
   </si>
   <si>
     <t>celestia1w2z74ln6kp08xac0smp2al35d7s7ju2rn5fuyj</t>
   </si>
   <si>
-    <t>celestia1wdnc6mfpcfs8md2cvm3gyfdzw8v3mcx8p2s6ux</t>
-  </si>
-  <si>
     <t>celestia1wwf8fsyr3xj8a84k5qkf0tkmvq8gmhg3ks8fdm</t>
   </si>
   <si>
@@ -127,6 +163,9 @@
     <t>celestia10guvn4243qg2l8ey8gy9zwttz6v23232f0rvcr</t>
   </si>
   <si>
+    <t>celestia1sdy2lhzh98xvv363da7xvg3jwlud9shcuj6k4w</t>
+  </si>
+  <si>
     <t>celestia1s6fd9nyr2n4dgcwa8elkq4j7fv0s5tn44ne59f</t>
   </si>
   <si>
@@ -172,85 +211,73 @@
     <t>celestia1n5hmum0fpuswq4nerff9rrwqudlylxxvjfrn4e</t>
   </si>
   <si>
+    <t>celestia15vwxwsex3ltadecjcxhg5zqkken63uvp2c7040</t>
+  </si>
+  <si>
     <t>celestia15scds0jq9crvvphgmnkxuvnycj64xj9lu8hnzg</t>
   </si>
   <si>
+    <t>celestia15epp26pl7cxhq6ff882cluyfxacj8lv5h44300</t>
+  </si>
+  <si>
     <t>celestia157qu9jpq3pasuc9s50tpd4hwu3tm45lrg6nm2q</t>
   </si>
   <si>
+    <t>celestia14pcyu8tnqed2z40y2qt9hy0u3xuetwgxsxh9hh</t>
+  </si>
+  <si>
     <t>celestia14a8ecps4lm2admgxdcq007kmgt4l9cxye4jv3w</t>
   </si>
   <si>
+    <t>celestia14l93dwnqe25rnu4anfc6q0dlcukea9pdwtkra7</t>
+  </si>
+  <si>
     <t>celestia1kw6mw70wafdxgp2n8s4lscx04du8ka6dvul6jy</t>
   </si>
   <si>
     <t>celestia1ksez8429rjftqa8f9wxxyg4l80ey7cfws3k6mw</t>
   </si>
   <si>
+    <t>celestia1kefzemyzcqfwfzhgg3g0hm4ccjpzllxhz0rfkt</t>
+  </si>
+  <si>
     <t>celestia1hy4s6pku897sq4s52mwd2wegvgd0llestm3ffm</t>
   </si>
   <si>
+    <t>celestia1h6e82vzacz2a2ewyr8rsu5hwtchvp225mtduqf</t>
+  </si>
+  <si>
     <t>celestia1cpxcvc7e6k4c0mxz3vf7w4jd5szd6ynq362h3p</t>
   </si>
   <si>
+    <t>celestia1c9mkft0d3sdjm3us883270veuww7qe3ydkuntu</t>
+  </si>
+  <si>
+    <t>celestia1c4skq47cqsyteg8kfjf6v3ehhza000ph8sky25</t>
+  </si>
+  <si>
     <t>celestia1c65g3f5ujul79f4tv39rnx4k3fp0nwvrp3w397</t>
   </si>
   <si>
     <t>celestia1ep7cpq9wa0cuds253ucwywqtl4ewx2y29zksfr</t>
   </si>
   <si>
+    <t>celestia1ezgrtr9xg5thqxst6chnfsa2w8p5sqe4856az5</t>
+  </si>
+  <si>
     <t>celestia1ege3jn6j509d7985jdefxtn7mcvngjp8qn9sk9</t>
   </si>
   <si>
+    <t>celestia1ekzawkkedhnlmxqcsp87aye5ne796jr43435as</t>
+  </si>
+  <si>
     <t>celestia1ehvppg4y9ar7dvnhjnqgjwxm2vd8yvsxpq6gre</t>
   </si>
   <si>
+    <t>celestia1emqzfcz5hezpg3z6ueqkptadpyx5qfujes34y6</t>
+  </si>
+  <si>
     <t>celestia16z62k22z3xpq7x9sdhwums2lcks8wejc02rdw7</t>
-  </si>
-  <si>
-    <t>celestia16e8eese68zg9yvsd9f8f4urywq9vt276k09l7l</t>
-  </si>
-  <si>
-    <t>celestia1mfje8fezn9mxc7dxnxzumr9kffhxtrn9e89l97</t>
-  </si>
-  <si>
-    <t>celestia1m20wyugxnse56q2lfmm9txyk2fx39s6fl9jxtk</t>
-  </si>
-  <si>
-    <t>celestia1mu26reayvd7vwknxugmx3vw8fqmvladjcfhtv2</t>
-  </si>
-  <si>
-    <t>celestia1mud3fuxt5zw4kfysd9gjrn6fjj5rz9g6z5txff</t>
-  </si>
-  <si>
-    <t>celestia1ux8zlvpsvmvnnrqxm0an2kff2rr7950cwa83v7</t>
-  </si>
-  <si>
-    <t>celestia1ujepumwuauf5dv4jjc686f6xj4u29rtp09yr70</t>
-  </si>
-  <si>
-    <t>celestia1uah45eeda8k5qwqdapslalxu8kgf9deqfuakr5</t>
-  </si>
-  <si>
-    <t>celestia1aqcxtsz2u66fq92et6txlwywtetg467j8ggrp0</t>
-  </si>
-  <si>
-    <t>celestia1a2de4qm0ecg338cyqmww3fpv9a7et9fgcnj0uh</t>
-  </si>
-  <si>
-    <t>celestia1a3858f250ve4t6rp9ef2svpr7sj20aax349dgr</t>
-  </si>
-  <si>
-    <t>celestia17p3r5sd5a0hctry733y4f7f5etp9uxvk2g4snz</t>
-  </si>
-  <si>
-    <t>celestia177n4ptnw3utwjlrk8n28t4zf00afm379ej5k60</t>
-  </si>
-  <si>
-    <t>celestia177h5g6har2ne9rhn5ekwlpgv7dtkjxp2765yfs</t>
-  </si>
-  <si>
-    <t>celestia1lft50ldy04u3szywhg38cnfpxfg7r5488veny2</t>
   </si>
 </sst>
 </file>
@@ -307,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -323,12 +350,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -342,6 +363,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4">
-        <v>28390.0</v>
+        <v>15941.0</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +594,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>271661.0</v>
+        <v>201485.0</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>310900.0</v>
+        <v>244903.0</v>
       </c>
     </row>
     <row r="5">
@@ -585,7 +610,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>31541.0</v>
+        <v>17711.0</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +618,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>28606.0</v>
+        <v>16408.0</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -602,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>15990.0</v>
+        <v>8979.0</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>66565.0</v>
+        <v>46788.0</v>
       </c>
     </row>
     <row r="9">
@@ -618,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>16562.0</v>
+        <v>11137.0</v>
       </c>
     </row>
     <row r="10">
@@ -626,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>64788.0</v>
+        <v>9300.0</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +659,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>15514.0</v>
+        <v>8711.0</v>
       </c>
     </row>
     <row r="12">
@@ -642,7 +667,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>16274.0</v>
+        <v>9138.0</v>
       </c>
     </row>
     <row r="13">
@@ -650,23 +675,23 @@
         <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>32358.0</v>
+        <v>100091.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5">
-        <v>1.5E7</v>
+      <c r="B14" s="4">
+        <v>18774.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5">
-        <v>1.5E7</v>
+      <c r="B15" s="4">
+        <v>895449.0</v>
       </c>
     </row>
     <row r="16">
@@ -674,7 +699,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>16620.0</v>
+        <v>1483638.0</v>
       </c>
     </row>
     <row r="17">
@@ -682,7 +707,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>23585.0</v>
+        <v>9333.0</v>
       </c>
     </row>
     <row r="18">
@@ -690,7 +715,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>41769.0</v>
+        <v>13244.0</v>
       </c>
     </row>
     <row r="19">
@@ -698,7 +723,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>19080.0</v>
+        <v>8849.0</v>
       </c>
     </row>
     <row r="20">
@@ -706,7 +731,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="4">
-        <v>31489.0</v>
+        <v>26908.0</v>
       </c>
     </row>
     <row r="21">
@@ -714,7 +739,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="4">
-        <v>42435.0</v>
+        <v>10714.0</v>
       </c>
     </row>
     <row r="22">
@@ -722,7 +747,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>51412.0</v>
+        <v>17716.0</v>
       </c>
     </row>
     <row r="23">
@@ -730,7 +755,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>18604.0</v>
+        <v>22360.0</v>
       </c>
     </row>
     <row r="24">
@@ -738,7 +763,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>15529.0</v>
+        <v>23828.0</v>
       </c>
     </row>
     <row r="25">
@@ -746,7 +771,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="4">
-        <v>16374.0</v>
+        <v>28869.0</v>
       </c>
     </row>
     <row r="26">
@@ -754,7 +779,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="4">
-        <v>153750.0</v>
+        <v>10446.0</v>
       </c>
     </row>
     <row r="27">
@@ -762,7 +787,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>33395.0</v>
+        <v>8720.0</v>
       </c>
     </row>
     <row r="28">
@@ -770,7 +795,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="4">
-        <v>30765.0</v>
+        <v>9238.0</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +803,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>55092.0</v>
+        <v>18268.0</v>
       </c>
     </row>
     <row r="30">
@@ -786,7 +811,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>463034.0</v>
+        <v>86333.0</v>
       </c>
     </row>
     <row r="31">
@@ -794,7 +819,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="4">
-        <v>416127.0</v>
+        <v>15972.0</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +827,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>15541.0</v>
+        <v>18752.0</v>
       </c>
     </row>
     <row r="33">
@@ -810,7 +835,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>17584.0</v>
+        <v>9243.0</v>
       </c>
     </row>
     <row r="34">
@@ -818,7 +843,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>19349.0</v>
+        <v>153365.0</v>
       </c>
     </row>
     <row r="35">
@@ -826,7 +851,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="4">
-        <v>23724.0</v>
+        <v>17275.0</v>
       </c>
     </row>
     <row r="36">
@@ -834,15 +859,15 @@
         <v>36</v>
       </c>
       <c r="B36" s="4">
-        <v>19988.0</v>
+        <v>12363.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5">
-        <v>1.5E7</v>
+      <c r="B37" s="4">
+        <v>9074.0</v>
       </c>
     </row>
     <row r="38">
@@ -850,7 +875,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>35363.0</v>
+        <v>31440.0</v>
       </c>
     </row>
     <row r="39">
@@ -858,7 +883,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="4">
-        <v>52275.0</v>
+        <v>260001.0</v>
       </c>
     </row>
     <row r="40">
@@ -866,7 +891,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="4">
-        <v>54658.0</v>
+        <v>88307.0</v>
       </c>
     </row>
     <row r="41">
@@ -874,7 +899,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="4">
-        <v>24311.0</v>
+        <v>235130.0</v>
       </c>
     </row>
     <row r="42">
@@ -882,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="4">
-        <v>43624.0</v>
+        <v>24150.0</v>
       </c>
     </row>
     <row r="43">
@@ -890,7 +915,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="4">
-        <v>50975.0</v>
+        <v>18278.0</v>
       </c>
     </row>
     <row r="44">
@@ -898,7 +923,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="4">
-        <v>19988.0</v>
+        <v>8633.0</v>
       </c>
     </row>
     <row r="45">
@@ -906,7 +931,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>84757.0</v>
+        <v>8727.0</v>
       </c>
     </row>
     <row r="46">
@@ -914,7 +939,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="4">
-        <v>116637.0</v>
+        <v>9874.0</v>
       </c>
     </row>
     <row r="47">
@@ -922,7 +947,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>61543.0</v>
+        <v>13321.0</v>
       </c>
     </row>
     <row r="48">
@@ -930,7 +955,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="4">
-        <v>33773.0</v>
+        <v>11223.0</v>
       </c>
     </row>
     <row r="49">
@@ -938,7 +963,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="4">
-        <v>24234.0</v>
+        <v>1107398.0</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +971,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="4">
-        <v>23555.0</v>
+        <v>9238.0</v>
       </c>
     </row>
     <row r="51">
@@ -954,7 +979,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="4">
-        <v>31741.0</v>
+        <v>19857.0</v>
       </c>
     </row>
     <row r="52">
@@ -962,7 +987,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="4">
-        <v>18744.0</v>
+        <v>31598.0</v>
       </c>
     </row>
     <row r="53">
@@ -970,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="4">
-        <v>46287.0</v>
+        <v>47958.0</v>
       </c>
     </row>
     <row r="54">
@@ -978,7 +1003,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="4">
-        <v>38222.0</v>
+        <v>13994.0</v>
       </c>
     </row>
     <row r="55">
@@ -986,7 +1011,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="4">
-        <v>33364.0</v>
+        <v>24875.0</v>
       </c>
     </row>
     <row r="56">
@@ -994,7 +1019,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="4">
-        <v>922743.0</v>
+        <v>28623.0</v>
       </c>
     </row>
     <row r="57">
@@ -1002,7 +1027,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>45027.0</v>
+        <v>11223.0</v>
       </c>
     </row>
     <row r="58">
@@ -1010,7 +1035,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="4">
-        <v>33553.0</v>
+        <v>51478.0</v>
       </c>
     </row>
     <row r="59">
@@ -1018,7 +1043,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="4">
-        <v>20295.0</v>
+        <v>65736.0</v>
       </c>
     </row>
     <row r="60">
@@ -1026,7 +1051,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="4">
-        <v>355239.0</v>
+        <v>45129.0</v>
       </c>
     </row>
     <row r="61">
@@ -1034,7 +1059,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="4">
-        <v>15673.0</v>
+        <v>19003.0</v>
       </c>
     </row>
     <row r="62">
@@ -1042,7 +1067,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="4">
-        <v>47137.0</v>
+        <v>13951.0</v>
       </c>
     </row>
     <row r="63">
@@ -1050,7 +1075,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="4">
-        <v>30781.0</v>
+        <v>13551.0</v>
       </c>
     </row>
     <row r="64">
@@ -1058,7 +1083,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="4">
-        <v>30838.0</v>
+        <v>17823.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1091,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="4">
-        <v>32635.0</v>
+        <v>10594.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1099,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="4">
-        <v>46125.0</v>
+        <v>10101.0</v>
       </c>
     </row>
     <row r="67">
@@ -1082,7 +1107,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="4">
-        <v>15898.0</v>
+        <v>26172.0</v>
       </c>
     </row>
     <row r="68">
@@ -1090,7 +1115,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="4">
-        <v>106157.0</v>
+        <v>28490.0</v>
       </c>
     </row>
     <row r="69">
@@ -1098,7 +1123,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="4">
-        <v>846064.0</v>
+        <v>21462.0</v>
       </c>
     </row>
     <row r="70">
@@ -1106,7 +1131,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="4">
-        <v>51245.0</v>
+        <v>10239.0</v>
       </c>
     </row>
     <row r="71">
@@ -1114,7 +1139,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="4">
-        <v>24666.0</v>
+        <v>34533.0</v>
       </c>
     </row>
     <row r="72">
@@ -1122,7 +1147,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="4">
-        <v>15831.0</v>
+        <v>31598.0</v>
       </c>
     </row>
     <row r="73">
@@ -1130,7 +1155,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="4">
-        <v>36023.0</v>
+        <v>518137.0</v>
       </c>
     </row>
     <row r="74">
@@ -1138,7 +1163,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="4">
-        <v>19834.0</v>
+        <v>25370.0</v>
       </c>
     </row>
     <row r="75">
@@ -1146,7 +1171,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="4">
-        <v>55086.0</v>
+        <v>43518.0</v>
       </c>
     </row>
     <row r="76">
@@ -1154,7 +1179,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="4">
-        <v>77691.0</v>
+        <v>18841.0</v>
       </c>
     </row>
     <row r="77">
@@ -1162,7 +1187,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="4">
-        <v>32541.0</v>
+        <v>10192.0</v>
       </c>
     </row>
     <row r="78">
@@ -1170,7 +1195,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="4">
-        <v>115602.0</v>
+        <v>11396.0</v>
       </c>
     </row>
     <row r="79">
@@ -1178,44 +1203,80 @@
         <v>79</v>
       </c>
       <c r="B79" s="4">
-        <v>171358.0</v>
+        <v>9091.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3"/>
-      <c r="B80" s="4"/>
+      <c r="A80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="4">
+        <v>28622.0</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="3"/>
-      <c r="B81" s="4"/>
+      <c r="A81" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="4">
+        <v>199560.0</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="3"/>
-      <c r="B82" s="4"/>
+      <c r="A82" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="4">
+        <v>8801.0</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="3"/>
-      <c r="B83" s="4"/>
+      <c r="A83" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="4">
+        <v>13934.0</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="3"/>
-      <c r="B84" s="4"/>
+      <c r="A84" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="4">
+        <v>30699.0</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="3"/>
-      <c r="B85" s="4"/>
+      <c r="A85" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" s="4">
+        <v>8646.0</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="3"/>
-      <c r="B86" s="4"/>
+      <c r="A86" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" s="4">
+        <v>17267.0</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="3"/>
-      <c r="B87" s="4"/>
+      <c r="A87" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="4">
+        <v>9924.0</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="3"/>
-      <c r="B88" s="4"/>
+      <c r="A88" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="4">
+        <v>17351.0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3"/>
@@ -1422,2996 +1483,3089 @@
       <c r="B139" s="4"/>
     </row>
     <row r="140">
-      <c r="A140" s="6"/>
+      <c r="A140" s="3"/>
       <c r="B140" s="4"/>
     </row>
     <row r="141">
-      <c r="A141" s="6"/>
+      <c r="A141" s="3"/>
       <c r="B141" s="4"/>
     </row>
     <row r="142">
-      <c r="A142" s="6"/>
+      <c r="A142" s="3"/>
       <c r="B142" s="4"/>
     </row>
     <row r="143">
-      <c r="A143" s="6"/>
+      <c r="A143" s="3"/>
       <c r="B143" s="4"/>
     </row>
     <row r="144">
-      <c r="A144" s="6"/>
+      <c r="A144" s="3"/>
       <c r="B144" s="4"/>
     </row>
     <row r="145">
-      <c r="A145" s="6"/>
+      <c r="A145" s="3"/>
       <c r="B145" s="4"/>
     </row>
     <row r="146">
-      <c r="A146" s="6"/>
+      <c r="A146" s="3"/>
       <c r="B146" s="4"/>
     </row>
     <row r="147">
-      <c r="A147" s="6"/>
+      <c r="A147" s="3"/>
       <c r="B147" s="4"/>
     </row>
     <row r="148">
-      <c r="A148" s="6"/>
+      <c r="A148" s="3"/>
       <c r="B148" s="4"/>
     </row>
     <row r="149">
-      <c r="A149" s="6"/>
+      <c r="A149" s="3"/>
       <c r="B149" s="4"/>
     </row>
     <row r="150">
-      <c r="A150" s="6"/>
+      <c r="A150" s="3"/>
       <c r="B150" s="4"/>
     </row>
     <row r="151">
-      <c r="A151" s="6"/>
+      <c r="A151" s="3"/>
       <c r="B151" s="4"/>
     </row>
     <row r="152">
-      <c r="A152" s="6"/>
+      <c r="A152" s="3"/>
       <c r="B152" s="4"/>
     </row>
     <row r="153">
-      <c r="A153" s="6"/>
+      <c r="A153" s="3"/>
       <c r="B153" s="4"/>
     </row>
     <row r="154">
-      <c r="A154" s="6"/>
+      <c r="A154" s="3"/>
       <c r="B154" s="4"/>
     </row>
     <row r="155">
-      <c r="A155" s="6"/>
+      <c r="A155" s="3"/>
       <c r="B155" s="4"/>
     </row>
     <row r="156">
-      <c r="A156" s="6"/>
+      <c r="A156" s="3"/>
       <c r="B156" s="4"/>
     </row>
     <row r="157">
-      <c r="A157" s="6"/>
+      <c r="A157" s="3"/>
       <c r="B157" s="4"/>
     </row>
     <row r="158">
-      <c r="A158" s="6"/>
+      <c r="A158" s="3"/>
       <c r="B158" s="4"/>
     </row>
     <row r="159">
-      <c r="A159" s="6"/>
+      <c r="A159" s="3"/>
       <c r="B159" s="4"/>
     </row>
     <row r="160">
-      <c r="A160" s="6"/>
+      <c r="A160" s="3"/>
       <c r="B160" s="4"/>
     </row>
     <row r="161">
-      <c r="A161" s="6"/>
+      <c r="A161" s="3"/>
       <c r="B161" s="4"/>
     </row>
     <row r="162">
-      <c r="A162" s="6"/>
+      <c r="A162" s="3"/>
       <c r="B162" s="4"/>
     </row>
     <row r="163">
-      <c r="A163" s="6"/>
+      <c r="A163" s="3"/>
       <c r="B163" s="4"/>
     </row>
     <row r="164">
-      <c r="A164" s="6"/>
+      <c r="A164" s="3"/>
       <c r="B164" s="4"/>
     </row>
     <row r="165">
-      <c r="A165" s="6"/>
+      <c r="A165" s="3"/>
       <c r="B165" s="4"/>
     </row>
     <row r="166">
-      <c r="A166" s="6"/>
+      <c r="A166" s="3"/>
       <c r="B166" s="4"/>
     </row>
     <row r="167">
-      <c r="A167" s="6"/>
+      <c r="A167" s="3"/>
       <c r="B167" s="4"/>
     </row>
     <row r="168">
-      <c r="A168" s="6"/>
+      <c r="A168" s="3"/>
       <c r="B168" s="4"/>
     </row>
     <row r="169">
-      <c r="A169" s="6"/>
+      <c r="A169" s="3"/>
       <c r="B169" s="4"/>
     </row>
     <row r="170">
-      <c r="A170" s="6"/>
+      <c r="A170" s="3"/>
       <c r="B170" s="4"/>
     </row>
     <row r="171">
-      <c r="A171" s="6"/>
+      <c r="A171" s="3"/>
       <c r="B171" s="4"/>
     </row>
     <row r="172">
-      <c r="A172" s="6"/>
+      <c r="A172" s="3"/>
       <c r="B172" s="4"/>
     </row>
     <row r="173">
-      <c r="A173" s="6"/>
+      <c r="A173" s="3"/>
       <c r="B173" s="4"/>
     </row>
     <row r="174">
-      <c r="A174" s="6"/>
+      <c r="A174" s="3"/>
       <c r="B174" s="4"/>
     </row>
     <row r="175">
-      <c r="A175" s="6"/>
+      <c r="A175" s="3"/>
       <c r="B175" s="4"/>
     </row>
     <row r="176">
-      <c r="A176" s="6"/>
+      <c r="A176" s="3"/>
       <c r="B176" s="4"/>
     </row>
     <row r="177">
-      <c r="A177" s="6"/>
+      <c r="A177" s="3"/>
       <c r="B177" s="4"/>
     </row>
     <row r="178">
-      <c r="A178" s="6"/>
+      <c r="A178" s="3"/>
       <c r="B178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="6"/>
+      <c r="A179" s="3"/>
       <c r="B179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="6"/>
+      <c r="A180" s="3"/>
       <c r="B180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="6"/>
+      <c r="A181" s="3"/>
       <c r="B181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="6"/>
+      <c r="A182" s="3"/>
       <c r="B182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="6"/>
+      <c r="A183" s="3"/>
       <c r="B183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="6"/>
+      <c r="A184" s="3"/>
       <c r="B184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="6"/>
+      <c r="A185" s="3"/>
       <c r="B185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="6"/>
+      <c r="A186" s="3"/>
       <c r="B186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="6"/>
+      <c r="A187" s="3"/>
       <c r="B187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="6"/>
+      <c r="A188" s="3"/>
       <c r="B188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="6"/>
+      <c r="A189" s="3"/>
       <c r="B189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="6"/>
+      <c r="A190" s="3"/>
       <c r="B190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="6"/>
+      <c r="A191" s="3"/>
       <c r="B191" s="4"/>
     </row>
     <row r="192">
-      <c r="A192" s="6"/>
+      <c r="A192" s="3"/>
       <c r="B192" s="4"/>
     </row>
     <row r="193">
-      <c r="A193" s="6"/>
+      <c r="A193" s="3"/>
       <c r="B193" s="4"/>
     </row>
     <row r="194">
-      <c r="A194" s="6"/>
+      <c r="A194" s="3"/>
       <c r="B194" s="4"/>
     </row>
     <row r="195">
-      <c r="A195" s="6"/>
+      <c r="A195" s="3"/>
       <c r="B195" s="4"/>
     </row>
     <row r="196">
-      <c r="A196" s="6"/>
+      <c r="A196" s="3"/>
       <c r="B196" s="4"/>
     </row>
     <row r="197">
-      <c r="A197" s="6"/>
+      <c r="A197" s="3"/>
       <c r="B197" s="4"/>
     </row>
     <row r="198">
-      <c r="A198" s="6"/>
+      <c r="A198" s="3"/>
       <c r="B198" s="4"/>
     </row>
     <row r="199">
-      <c r="A199" s="6"/>
+      <c r="A199" s="3"/>
       <c r="B199" s="4"/>
     </row>
     <row r="200">
-      <c r="A200" s="6"/>
+      <c r="A200" s="3"/>
       <c r="B200" s="4"/>
     </row>
     <row r="201">
-      <c r="A201" s="6"/>
+      <c r="A201" s="3"/>
       <c r="B201" s="4"/>
     </row>
     <row r="202">
-      <c r="A202" s="6"/>
+      <c r="A202" s="3"/>
       <c r="B202" s="4"/>
     </row>
     <row r="203">
-      <c r="A203" s="6"/>
+      <c r="A203" s="3"/>
       <c r="B203" s="4"/>
     </row>
     <row r="204">
-      <c r="A204" s="6"/>
+      <c r="A204" s="3"/>
       <c r="B204" s="4"/>
     </row>
     <row r="205">
-      <c r="A205" s="6"/>
+      <c r="A205" s="3"/>
       <c r="B205" s="4"/>
     </row>
     <row r="206">
-      <c r="A206" s="6"/>
+      <c r="A206" s="3"/>
       <c r="B206" s="4"/>
     </row>
     <row r="207">
-      <c r="A207" s="6"/>
+      <c r="A207" s="3"/>
       <c r="B207" s="4"/>
     </row>
     <row r="208">
-      <c r="A208" s="6"/>
+      <c r="A208" s="3"/>
       <c r="B208" s="4"/>
     </row>
     <row r="209">
-      <c r="A209" s="6"/>
+      <c r="A209" s="3"/>
       <c r="B209" s="4"/>
     </row>
     <row r="210">
-      <c r="A210" s="6"/>
+      <c r="A210" s="3"/>
       <c r="B210" s="4"/>
     </row>
     <row r="211">
-      <c r="A211" s="6"/>
+      <c r="A211" s="3"/>
       <c r="B211" s="4"/>
     </row>
     <row r="212">
-      <c r="A212" s="6"/>
+      <c r="A212" s="3"/>
       <c r="B212" s="4"/>
     </row>
     <row r="213">
-      <c r="A213" s="6"/>
+      <c r="A213" s="3"/>
       <c r="B213" s="4"/>
     </row>
     <row r="214">
-      <c r="A214" s="6"/>
+      <c r="A214" s="3"/>
       <c r="B214" s="4"/>
     </row>
     <row r="215">
-      <c r="A215" s="6"/>
+      <c r="A215" s="3"/>
       <c r="B215" s="4"/>
     </row>
     <row r="216">
-      <c r="A216" s="6"/>
+      <c r="A216" s="3"/>
       <c r="B216" s="4"/>
     </row>
     <row r="217">
-      <c r="A217" s="6"/>
+      <c r="A217" s="3"/>
       <c r="B217" s="4"/>
     </row>
     <row r="218">
-      <c r="A218" s="6"/>
+      <c r="A218" s="3"/>
       <c r="B218" s="4"/>
     </row>
     <row r="219">
-      <c r="A219" s="6"/>
+      <c r="A219" s="3"/>
       <c r="B219" s="4"/>
     </row>
     <row r="220">
-      <c r="A220" s="6"/>
+      <c r="A220" s="3"/>
       <c r="B220" s="4"/>
     </row>
     <row r="221">
-      <c r="A221" s="6"/>
+      <c r="A221" s="3"/>
       <c r="B221" s="4"/>
     </row>
     <row r="222">
-      <c r="A222" s="6"/>
+      <c r="A222" s="3"/>
       <c r="B222" s="4"/>
     </row>
     <row r="223">
-      <c r="A223" s="6"/>
+      <c r="A223" s="3"/>
       <c r="B223" s="4"/>
     </row>
     <row r="224">
-      <c r="A224" s="6"/>
+      <c r="A224" s="3"/>
       <c r="B224" s="4"/>
     </row>
     <row r="225">
-      <c r="A225" s="6"/>
+      <c r="A225" s="3"/>
       <c r="B225" s="4"/>
     </row>
     <row r="226">
-      <c r="A226" s="6"/>
+      <c r="A226" s="3"/>
       <c r="B226" s="4"/>
     </row>
     <row r="227">
-      <c r="A227" s="6"/>
+      <c r="A227" s="3"/>
       <c r="B227" s="4"/>
     </row>
     <row r="228">
-      <c r="A228" s="6"/>
+      <c r="A228" s="3"/>
       <c r="B228" s="4"/>
     </row>
     <row r="229">
-      <c r="A229" s="6"/>
+      <c r="A229" s="3"/>
       <c r="B229" s="4"/>
     </row>
     <row r="230">
-      <c r="A230" s="6"/>
+      <c r="A230" s="3"/>
       <c r="B230" s="4"/>
     </row>
     <row r="231">
-      <c r="A231" s="6"/>
+      <c r="A231" s="3"/>
       <c r="B231" s="4"/>
     </row>
     <row r="232">
-      <c r="A232" s="6"/>
+      <c r="A232" s="3"/>
       <c r="B232" s="4"/>
     </row>
     <row r="233">
-      <c r="A233" s="6"/>
+      <c r="A233" s="3"/>
       <c r="B233" s="4"/>
     </row>
     <row r="234">
-      <c r="A234" s="6"/>
+      <c r="A234" s="3"/>
       <c r="B234" s="4"/>
     </row>
     <row r="235">
-      <c r="A235" s="6"/>
+      <c r="A235" s="3"/>
       <c r="B235" s="4"/>
     </row>
     <row r="236">
-      <c r="A236" s="6"/>
+      <c r="A236" s="3"/>
       <c r="B236" s="4"/>
     </row>
     <row r="237">
-      <c r="A237" s="6"/>
+      <c r="A237" s="3"/>
       <c r="B237" s="4"/>
     </row>
     <row r="238">
-      <c r="A238" s="6"/>
+      <c r="A238" s="3"/>
       <c r="B238" s="4"/>
     </row>
     <row r="239">
-      <c r="A239" s="6"/>
+      <c r="A239" s="3"/>
       <c r="B239" s="4"/>
     </row>
     <row r="240">
-      <c r="A240" s="6"/>
+      <c r="A240" s="3"/>
       <c r="B240" s="4"/>
     </row>
     <row r="241">
-      <c r="A241" s="6"/>
+      <c r="A241" s="3"/>
       <c r="B241" s="4"/>
     </row>
     <row r="242">
-      <c r="A242" s="6"/>
+      <c r="A242" s="3"/>
       <c r="B242" s="4"/>
     </row>
     <row r="243">
-      <c r="A243" s="6"/>
+      <c r="A243" s="3"/>
       <c r="B243" s="4"/>
     </row>
     <row r="244">
-      <c r="A244" s="6"/>
+      <c r="A244" s="3"/>
       <c r="B244" s="4"/>
     </row>
     <row r="245">
-      <c r="A245" s="6"/>
+      <c r="A245" s="3"/>
       <c r="B245" s="4"/>
     </row>
     <row r="246">
-      <c r="A246" s="6"/>
+      <c r="A246" s="3"/>
       <c r="B246" s="4"/>
     </row>
     <row r="247">
-      <c r="A247" s="6"/>
+      <c r="A247" s="3"/>
       <c r="B247" s="4"/>
     </row>
     <row r="248">
-      <c r="A248" s="6"/>
+      <c r="A248" s="3"/>
       <c r="B248" s="4"/>
     </row>
     <row r="249">
-      <c r="A249" s="6"/>
+      <c r="A249" s="3"/>
       <c r="B249" s="4"/>
     </row>
     <row r="250">
-      <c r="A250" s="6"/>
+      <c r="A250" s="3"/>
       <c r="B250" s="4"/>
     </row>
     <row r="251">
-      <c r="A251" s="6"/>
+      <c r="A251" s="3"/>
       <c r="B251" s="4"/>
     </row>
     <row r="252">
-      <c r="A252" s="6"/>
+      <c r="A252" s="3"/>
       <c r="B252" s="4"/>
     </row>
     <row r="253">
-      <c r="A253" s="6"/>
+      <c r="A253" s="3"/>
       <c r="B253" s="4"/>
     </row>
     <row r="254">
-      <c r="A254" s="6"/>
+      <c r="A254" s="3"/>
       <c r="B254" s="4"/>
     </row>
     <row r="255">
-      <c r="A255" s="6"/>
+      <c r="A255" s="3"/>
       <c r="B255" s="4"/>
     </row>
     <row r="256">
-      <c r="A256" s="6"/>
+      <c r="A256" s="3"/>
       <c r="B256" s="4"/>
     </row>
     <row r="257">
-      <c r="A257" s="6"/>
+      <c r="A257" s="3"/>
       <c r="B257" s="4"/>
     </row>
     <row r="258">
-      <c r="A258" s="6"/>
+      <c r="A258" s="3"/>
       <c r="B258" s="4"/>
     </row>
     <row r="259">
-      <c r="A259" s="6"/>
+      <c r="A259" s="3"/>
       <c r="B259" s="4"/>
     </row>
     <row r="260">
-      <c r="A260" s="6"/>
+      <c r="A260" s="3"/>
       <c r="B260" s="4"/>
     </row>
     <row r="261">
-      <c r="A261" s="6"/>
+      <c r="A261" s="3"/>
       <c r="B261" s="4"/>
     </row>
     <row r="262">
-      <c r="A262" s="6"/>
+      <c r="A262" s="3"/>
       <c r="B262" s="4"/>
     </row>
     <row r="263">
-      <c r="A263" s="6"/>
+      <c r="A263" s="3"/>
       <c r="B263" s="4"/>
     </row>
     <row r="264">
-      <c r="A264" s="6"/>
+      <c r="A264" s="3"/>
       <c r="B264" s="4"/>
     </row>
     <row r="265">
-      <c r="A265" s="6"/>
+      <c r="A265" s="3"/>
       <c r="B265" s="4"/>
     </row>
     <row r="266">
-      <c r="A266" s="6"/>
+      <c r="A266" s="3"/>
       <c r="B266" s="4"/>
     </row>
     <row r="267">
-      <c r="A267" s="6"/>
+      <c r="A267" s="3"/>
       <c r="B267" s="4"/>
     </row>
     <row r="268">
-      <c r="A268" s="6"/>
+      <c r="A268" s="3"/>
       <c r="B268" s="4"/>
     </row>
     <row r="269">
-      <c r="A269" s="6"/>
+      <c r="A269" s="3"/>
       <c r="B269" s="4"/>
     </row>
     <row r="270">
-      <c r="A270" s="6"/>
+      <c r="A270" s="3"/>
       <c r="B270" s="4"/>
     </row>
     <row r="271">
-      <c r="A271" s="6"/>
+      <c r="A271" s="3"/>
       <c r="B271" s="4"/>
     </row>
     <row r="272">
-      <c r="A272" s="6"/>
+      <c r="A272" s="3"/>
       <c r="B272" s="4"/>
     </row>
     <row r="273">
-      <c r="A273" s="6"/>
+      <c r="A273" s="3"/>
       <c r="B273" s="4"/>
     </row>
     <row r="274">
-      <c r="A274" s="6"/>
+      <c r="A274" s="3"/>
       <c r="B274" s="4"/>
     </row>
     <row r="275">
-      <c r="A275" s="6"/>
+      <c r="A275" s="3"/>
       <c r="B275" s="4"/>
     </row>
     <row r="276">
-      <c r="A276" s="6"/>
+      <c r="A276" s="3"/>
       <c r="B276" s="4"/>
     </row>
     <row r="277">
-      <c r="A277" s="6"/>
+      <c r="A277" s="3"/>
       <c r="B277" s="4"/>
     </row>
     <row r="278">
-      <c r="A278" s="6"/>
+      <c r="A278" s="3"/>
       <c r="B278" s="4"/>
     </row>
     <row r="279">
-      <c r="A279" s="6"/>
+      <c r="A279" s="3"/>
       <c r="B279" s="4"/>
     </row>
     <row r="280">
-      <c r="A280" s="6"/>
+      <c r="A280" s="3"/>
       <c r="B280" s="4"/>
     </row>
     <row r="281">
-      <c r="A281" s="6"/>
+      <c r="A281" s="3"/>
       <c r="B281" s="4"/>
     </row>
     <row r="282">
-      <c r="A282" s="6"/>
+      <c r="A282" s="3"/>
       <c r="B282" s="4"/>
     </row>
     <row r="283">
-      <c r="A283" s="6"/>
+      <c r="A283" s="3"/>
       <c r="B283" s="4"/>
     </row>
     <row r="284">
-      <c r="A284" s="6"/>
+      <c r="A284" s="3"/>
       <c r="B284" s="4"/>
     </row>
     <row r="285">
-      <c r="A285" s="6"/>
+      <c r="A285" s="3"/>
       <c r="B285" s="4"/>
     </row>
     <row r="286">
-      <c r="A286" s="6"/>
+      <c r="A286" s="3"/>
       <c r="B286" s="4"/>
     </row>
     <row r="287">
-      <c r="A287" s="6"/>
+      <c r="A287" s="3"/>
       <c r="B287" s="4"/>
     </row>
     <row r="288">
-      <c r="A288" s="6"/>
+      <c r="A288" s="3"/>
       <c r="B288" s="4"/>
     </row>
     <row r="289">
-      <c r="A289" s="6"/>
+      <c r="A289" s="3"/>
       <c r="B289" s="4"/>
     </row>
     <row r="290">
-      <c r="A290" s="6"/>
+      <c r="A290" s="3"/>
       <c r="B290" s="4"/>
     </row>
     <row r="291">
-      <c r="A291" s="6"/>
+      <c r="A291" s="3"/>
       <c r="B291" s="4"/>
     </row>
     <row r="292">
-      <c r="A292" s="6"/>
+      <c r="A292" s="3"/>
       <c r="B292" s="4"/>
     </row>
     <row r="293">
-      <c r="A293" s="6"/>
+      <c r="A293" s="3"/>
       <c r="B293" s="4"/>
     </row>
     <row r="294">
-      <c r="A294" s="6"/>
+      <c r="A294" s="3"/>
       <c r="B294" s="4"/>
     </row>
     <row r="295">
-      <c r="A295" s="6"/>
+      <c r="A295" s="3"/>
       <c r="B295" s="4"/>
     </row>
     <row r="296">
-      <c r="A296" s="6"/>
+      <c r="A296" s="3"/>
       <c r="B296" s="4"/>
     </row>
     <row r="297">
-      <c r="A297" s="6"/>
+      <c r="A297" s="3"/>
       <c r="B297" s="4"/>
     </row>
     <row r="298">
-      <c r="A298" s="6"/>
+      <c r="A298" s="3"/>
       <c r="B298" s="4"/>
     </row>
     <row r="299">
-      <c r="A299" s="6"/>
+      <c r="A299" s="3"/>
       <c r="B299" s="4"/>
     </row>
     <row r="300">
-      <c r="A300" s="6"/>
+      <c r="A300" s="3"/>
       <c r="B300" s="4"/>
     </row>
     <row r="301">
-      <c r="A301" s="6"/>
+      <c r="A301" s="3"/>
       <c r="B301" s="4"/>
     </row>
     <row r="302">
-      <c r="A302" s="6"/>
+      <c r="A302" s="3"/>
       <c r="B302" s="4"/>
     </row>
     <row r="303">
-      <c r="A303" s="6"/>
+      <c r="A303" s="3"/>
       <c r="B303" s="4"/>
     </row>
     <row r="304">
-      <c r="A304" s="6"/>
+      <c r="A304" s="3"/>
       <c r="B304" s="4"/>
     </row>
     <row r="305">
-      <c r="A305" s="6"/>
+      <c r="A305" s="3"/>
       <c r="B305" s="4"/>
     </row>
     <row r="306">
-      <c r="A306" s="6"/>
+      <c r="A306" s="3"/>
       <c r="B306" s="4"/>
     </row>
     <row r="307">
-      <c r="A307" s="6"/>
+      <c r="A307" s="3"/>
       <c r="B307" s="4"/>
     </row>
     <row r="308">
-      <c r="A308" s="6"/>
+      <c r="A308" s="3"/>
       <c r="B308" s="4"/>
     </row>
     <row r="309">
-      <c r="A309" s="6"/>
+      <c r="A309" s="3"/>
       <c r="B309" s="4"/>
     </row>
     <row r="310">
-      <c r="A310" s="6"/>
+      <c r="A310" s="3"/>
       <c r="B310" s="4"/>
     </row>
     <row r="311">
-      <c r="A311" s="6"/>
+      <c r="A311" s="3"/>
       <c r="B311" s="4"/>
     </row>
     <row r="312">
-      <c r="A312" s="6"/>
+      <c r="A312" s="3"/>
       <c r="B312" s="4"/>
     </row>
     <row r="313">
-      <c r="A313" s="6"/>
+      <c r="A313" s="3"/>
       <c r="B313" s="4"/>
     </row>
     <row r="314">
-      <c r="A314" s="6"/>
+      <c r="A314" s="3"/>
       <c r="B314" s="4"/>
     </row>
     <row r="315">
-      <c r="A315" s="6"/>
+      <c r="A315" s="3"/>
       <c r="B315" s="4"/>
     </row>
     <row r="316">
-      <c r="A316" s="6"/>
+      <c r="A316" s="3"/>
       <c r="B316" s="4"/>
     </row>
     <row r="317">
-      <c r="A317" s="6"/>
+      <c r="A317" s="3"/>
       <c r="B317" s="4"/>
     </row>
     <row r="318">
-      <c r="A318" s="6"/>
+      <c r="A318" s="3"/>
       <c r="B318" s="4"/>
     </row>
     <row r="319">
-      <c r="A319" s="6"/>
+      <c r="A319" s="3"/>
       <c r="B319" s="4"/>
     </row>
     <row r="320">
-      <c r="A320" s="6"/>
+      <c r="A320" s="3"/>
       <c r="B320" s="4"/>
     </row>
     <row r="321">
-      <c r="A321" s="6"/>
+      <c r="A321" s="3"/>
       <c r="B321" s="4"/>
     </row>
     <row r="322">
-      <c r="A322" s="6"/>
+      <c r="A322" s="3"/>
       <c r="B322" s="4"/>
     </row>
     <row r="323">
-      <c r="A323" s="6"/>
+      <c r="A323" s="3"/>
       <c r="B323" s="4"/>
     </row>
     <row r="324">
-      <c r="A324" s="6"/>
+      <c r="A324" s="3"/>
       <c r="B324" s="4"/>
     </row>
     <row r="325">
-      <c r="A325" s="6"/>
+      <c r="A325" s="3"/>
       <c r="B325" s="4"/>
     </row>
     <row r="326">
-      <c r="A326" s="6"/>
+      <c r="A326" s="3"/>
       <c r="B326" s="4"/>
     </row>
     <row r="327">
-      <c r="A327" s="6"/>
+      <c r="A327" s="3"/>
       <c r="B327" s="4"/>
     </row>
     <row r="328">
-      <c r="A328" s="6"/>
+      <c r="A328" s="3"/>
       <c r="B328" s="4"/>
     </row>
     <row r="329">
-      <c r="A329" s="6"/>
+      <c r="A329" s="3"/>
       <c r="B329" s="4"/>
     </row>
     <row r="330">
-      <c r="A330" s="6"/>
+      <c r="A330" s="3"/>
       <c r="B330" s="4"/>
     </row>
     <row r="331">
-      <c r="A331" s="6"/>
+      <c r="A331" s="3"/>
       <c r="B331" s="4"/>
     </row>
     <row r="332">
-      <c r="A332" s="6"/>
+      <c r="A332" s="3"/>
       <c r="B332" s="4"/>
     </row>
     <row r="333">
-      <c r="A333" s="6"/>
+      <c r="A333" s="3"/>
       <c r="B333" s="4"/>
     </row>
     <row r="334">
-      <c r="A334" s="6"/>
+      <c r="A334" s="3"/>
       <c r="B334" s="4"/>
     </row>
     <row r="335">
-      <c r="A335" s="6"/>
+      <c r="A335" s="3"/>
       <c r="B335" s="4"/>
     </row>
     <row r="336">
-      <c r="A336" s="6"/>
+      <c r="A336" s="3"/>
       <c r="B336" s="4"/>
     </row>
     <row r="337">
-      <c r="A337" s="6"/>
+      <c r="A337" s="3"/>
       <c r="B337" s="4"/>
     </row>
     <row r="338">
-      <c r="A338" s="6"/>
+      <c r="A338" s="3"/>
       <c r="B338" s="4"/>
     </row>
     <row r="339">
-      <c r="A339" s="6"/>
+      <c r="A339" s="3"/>
       <c r="B339" s="4"/>
     </row>
     <row r="340">
-      <c r="A340" s="6"/>
+      <c r="A340" s="3"/>
       <c r="B340" s="4"/>
     </row>
     <row r="341">
-      <c r="A341" s="6"/>
+      <c r="A341" s="3"/>
       <c r="B341" s="4"/>
     </row>
     <row r="342">
-      <c r="A342" s="6"/>
+      <c r="A342" s="3"/>
       <c r="B342" s="4"/>
     </row>
     <row r="343">
-      <c r="A343" s="6"/>
+      <c r="A343" s="3"/>
       <c r="B343" s="4"/>
     </row>
     <row r="344">
-      <c r="A344" s="6"/>
+      <c r="A344" s="3"/>
       <c r="B344" s="4"/>
     </row>
     <row r="345">
-      <c r="A345" s="6"/>
+      <c r="A345" s="3"/>
       <c r="B345" s="4"/>
     </row>
     <row r="346">
-      <c r="A346" s="6"/>
+      <c r="A346" s="3"/>
       <c r="B346" s="4"/>
     </row>
     <row r="347">
-      <c r="A347" s="6"/>
+      <c r="A347" s="3"/>
       <c r="B347" s="4"/>
     </row>
     <row r="348">
-      <c r="A348" s="6"/>
+      <c r="A348" s="3"/>
       <c r="B348" s="4"/>
     </row>
     <row r="349">
-      <c r="A349" s="6"/>
+      <c r="A349" s="3"/>
       <c r="B349" s="4"/>
     </row>
     <row r="350">
-      <c r="A350" s="6"/>
+      <c r="A350" s="3"/>
       <c r="B350" s="4"/>
     </row>
     <row r="351">
-      <c r="A351" s="6"/>
+      <c r="A351" s="3"/>
       <c r="B351" s="4"/>
     </row>
     <row r="352">
-      <c r="A352" s="6"/>
+      <c r="A352" s="3"/>
       <c r="B352" s="4"/>
     </row>
     <row r="353">
-      <c r="A353" s="6"/>
+      <c r="A353" s="3"/>
       <c r="B353" s="4"/>
     </row>
     <row r="354">
-      <c r="A354" s="6"/>
+      <c r="A354" s="3"/>
       <c r="B354" s="4"/>
     </row>
     <row r="355">
-      <c r="A355" s="6"/>
+      <c r="A355" s="3"/>
       <c r="B355" s="4"/>
     </row>
     <row r="356">
-      <c r="A356" s="6"/>
+      <c r="A356" s="3"/>
       <c r="B356" s="4"/>
     </row>
     <row r="357">
-      <c r="A357" s="6"/>
+      <c r="A357" s="3"/>
       <c r="B357" s="4"/>
     </row>
     <row r="358">
-      <c r="A358" s="6"/>
+      <c r="A358" s="3"/>
       <c r="B358" s="4"/>
     </row>
     <row r="359">
-      <c r="A359" s="6"/>
+      <c r="A359" s="3"/>
       <c r="B359" s="4"/>
     </row>
     <row r="360">
-      <c r="A360" s="6"/>
+      <c r="A360" s="3"/>
       <c r="B360" s="4"/>
     </row>
     <row r="361">
-      <c r="A361" s="6"/>
+      <c r="A361" s="3"/>
       <c r="B361" s="4"/>
     </row>
     <row r="362">
-      <c r="A362" s="6"/>
+      <c r="A362" s="3"/>
       <c r="B362" s="4"/>
     </row>
     <row r="363">
-      <c r="A363" s="6"/>
+      <c r="A363" s="3"/>
       <c r="B363" s="4"/>
     </row>
     <row r="364">
-      <c r="A364" s="6"/>
+      <c r="A364" s="3"/>
       <c r="B364" s="4"/>
     </row>
     <row r="365">
-      <c r="A365" s="6"/>
+      <c r="A365" s="3"/>
       <c r="B365" s="4"/>
     </row>
     <row r="366">
-      <c r="A366" s="6"/>
+      <c r="A366" s="3"/>
       <c r="B366" s="4"/>
     </row>
     <row r="367">
-      <c r="A367" s="6"/>
+      <c r="A367" s="3"/>
       <c r="B367" s="4"/>
     </row>
     <row r="368">
-      <c r="A368" s="6"/>
+      <c r="A368" s="3"/>
       <c r="B368" s="4"/>
     </row>
     <row r="369">
-      <c r="A369" s="6"/>
+      <c r="A369" s="3"/>
       <c r="B369" s="4"/>
     </row>
     <row r="370">
-      <c r="A370" s="6"/>
+      <c r="A370" s="3"/>
       <c r="B370" s="4"/>
     </row>
     <row r="371">
-      <c r="A371" s="6"/>
+      <c r="A371" s="3"/>
       <c r="B371" s="4"/>
     </row>
     <row r="372">
-      <c r="A372" s="6"/>
+      <c r="A372" s="3"/>
       <c r="B372" s="4"/>
     </row>
     <row r="373">
-      <c r="A373" s="6"/>
+      <c r="A373" s="3"/>
       <c r="B373" s="4"/>
     </row>
     <row r="374">
-      <c r="A374" s="6"/>
+      <c r="A374" s="3"/>
       <c r="B374" s="4"/>
     </row>
     <row r="375">
-      <c r="A375" s="6"/>
+      <c r="A375" s="3"/>
       <c r="B375" s="4"/>
     </row>
     <row r="376">
-      <c r="A376" s="6"/>
+      <c r="A376" s="3"/>
       <c r="B376" s="4"/>
     </row>
     <row r="377">
-      <c r="A377" s="6"/>
+      <c r="A377" s="3"/>
       <c r="B377" s="4"/>
     </row>
     <row r="378">
-      <c r="A378" s="6"/>
+      <c r="A378" s="3"/>
       <c r="B378" s="4"/>
     </row>
     <row r="379">
-      <c r="A379" s="6"/>
+      <c r="A379" s="3"/>
       <c r="B379" s="4"/>
     </row>
     <row r="380">
-      <c r="A380" s="6"/>
+      <c r="A380" s="3"/>
       <c r="B380" s="4"/>
     </row>
     <row r="381">
-      <c r="A381" s="6"/>
+      <c r="A381" s="3"/>
       <c r="B381" s="4"/>
     </row>
     <row r="382">
-      <c r="A382" s="6"/>
+      <c r="A382" s="3"/>
       <c r="B382" s="4"/>
     </row>
     <row r="383">
-      <c r="A383" s="6"/>
+      <c r="A383" s="3"/>
       <c r="B383" s="4"/>
     </row>
     <row r="384">
-      <c r="A384" s="6"/>
+      <c r="A384" s="3"/>
       <c r="B384" s="4"/>
     </row>
     <row r="385">
-      <c r="A385" s="6"/>
+      <c r="A385" s="3"/>
       <c r="B385" s="4"/>
     </row>
     <row r="386">
-      <c r="A386" s="6"/>
+      <c r="A386" s="3"/>
       <c r="B386" s="4"/>
     </row>
     <row r="387">
-      <c r="A387" s="6"/>
+      <c r="A387" s="3"/>
       <c r="B387" s="4"/>
     </row>
     <row r="388">
-      <c r="A388" s="6"/>
+      <c r="A388" s="3"/>
       <c r="B388" s="4"/>
     </row>
     <row r="389">
-      <c r="A389" s="6"/>
+      <c r="A389" s="3"/>
       <c r="B389" s="4"/>
     </row>
     <row r="390">
-      <c r="A390" s="6"/>
+      <c r="A390" s="3"/>
       <c r="B390" s="4"/>
     </row>
     <row r="391">
-      <c r="A391" s="6"/>
+      <c r="A391" s="3"/>
       <c r="B391" s="4"/>
     </row>
     <row r="392">
-      <c r="A392" s="6"/>
+      <c r="A392" s="3"/>
       <c r="B392" s="4"/>
     </row>
     <row r="393">
-      <c r="A393" s="6"/>
+      <c r="A393" s="3"/>
       <c r="B393" s="4"/>
     </row>
     <row r="394">
-      <c r="A394" s="6"/>
+      <c r="A394" s="3"/>
       <c r="B394" s="4"/>
     </row>
     <row r="395">
-      <c r="A395" s="6"/>
+      <c r="A395" s="3"/>
       <c r="B395" s="4"/>
     </row>
     <row r="396">
-      <c r="A396" s="6"/>
+      <c r="A396" s="3"/>
       <c r="B396" s="4"/>
     </row>
     <row r="397">
-      <c r="A397" s="6"/>
+      <c r="A397" s="3"/>
       <c r="B397" s="4"/>
     </row>
     <row r="398">
-      <c r="A398" s="6"/>
+      <c r="A398" s="3"/>
       <c r="B398" s="4"/>
     </row>
     <row r="399">
-      <c r="A399" s="6"/>
+      <c r="A399" s="3"/>
       <c r="B399" s="4"/>
     </row>
     <row r="400">
-      <c r="A400" s="6"/>
+      <c r="A400" s="3"/>
       <c r="B400" s="4"/>
     </row>
     <row r="401">
-      <c r="A401" s="6"/>
+      <c r="A401" s="3"/>
       <c r="B401" s="4"/>
     </row>
     <row r="402">
-      <c r="A402" s="6"/>
+      <c r="A402" s="3"/>
       <c r="B402" s="4"/>
     </row>
     <row r="403">
-      <c r="A403" s="6"/>
+      <c r="A403" s="3"/>
       <c r="B403" s="4"/>
     </row>
     <row r="404">
-      <c r="A404" s="6"/>
+      <c r="A404" s="3"/>
       <c r="B404" s="4"/>
     </row>
     <row r="405">
-      <c r="A405" s="6"/>
+      <c r="A405" s="3"/>
       <c r="B405" s="4"/>
     </row>
     <row r="406">
-      <c r="A406" s="6"/>
+      <c r="A406" s="3"/>
       <c r="B406" s="4"/>
     </row>
     <row r="407">
-      <c r="A407" s="6"/>
+      <c r="A407" s="3"/>
       <c r="B407" s="4"/>
     </row>
     <row r="408">
-      <c r="A408" s="6"/>
+      <c r="A408" s="3"/>
       <c r="B408" s="4"/>
     </row>
     <row r="409">
-      <c r="A409" s="6"/>
+      <c r="A409" s="3"/>
       <c r="B409" s="4"/>
     </row>
     <row r="410">
-      <c r="A410" s="6"/>
+      <c r="A410" s="3"/>
       <c r="B410" s="4"/>
     </row>
     <row r="411">
-      <c r="A411" s="6"/>
+      <c r="A411" s="3"/>
       <c r="B411" s="4"/>
     </row>
     <row r="412">
-      <c r="A412" s="6"/>
+      <c r="A412" s="3"/>
       <c r="B412" s="4"/>
     </row>
     <row r="413">
-      <c r="A413" s="6"/>
+      <c r="A413" s="3"/>
       <c r="B413" s="4"/>
     </row>
     <row r="414">
-      <c r="A414" s="6"/>
+      <c r="A414" s="3"/>
       <c r="B414" s="4"/>
     </row>
     <row r="415">
-      <c r="A415" s="6"/>
+      <c r="A415" s="3"/>
       <c r="B415" s="4"/>
     </row>
     <row r="416">
-      <c r="A416" s="6"/>
+      <c r="A416" s="3"/>
       <c r="B416" s="4"/>
     </row>
     <row r="417">
-      <c r="A417" s="6"/>
+      <c r="A417" s="3"/>
       <c r="B417" s="4"/>
     </row>
     <row r="418">
-      <c r="A418" s="6"/>
+      <c r="A418" s="3"/>
       <c r="B418" s="4"/>
     </row>
     <row r="419">
-      <c r="A419" s="6"/>
+      <c r="A419" s="3"/>
       <c r="B419" s="4"/>
     </row>
     <row r="420">
-      <c r="A420" s="6"/>
+      <c r="A420" s="3"/>
       <c r="B420" s="4"/>
     </row>
     <row r="421">
-      <c r="A421" s="6"/>
+      <c r="A421" s="3"/>
       <c r="B421" s="4"/>
     </row>
     <row r="422">
-      <c r="A422" s="6"/>
+      <c r="A422" s="3"/>
       <c r="B422" s="4"/>
     </row>
     <row r="423">
-      <c r="A423" s="6"/>
+      <c r="A423" s="3"/>
       <c r="B423" s="4"/>
     </row>
     <row r="424">
-      <c r="A424" s="6"/>
+      <c r="A424" s="3"/>
       <c r="B424" s="4"/>
     </row>
     <row r="425">
-      <c r="A425" s="6"/>
+      <c r="A425" s="3"/>
       <c r="B425" s="4"/>
     </row>
     <row r="426">
-      <c r="A426" s="6"/>
+      <c r="A426" s="3"/>
       <c r="B426" s="4"/>
     </row>
     <row r="427">
-      <c r="A427" s="6"/>
+      <c r="A427" s="3"/>
       <c r="B427" s="4"/>
     </row>
     <row r="428">
-      <c r="A428" s="6"/>
+      <c r="A428" s="3"/>
       <c r="B428" s="4"/>
     </row>
     <row r="429">
-      <c r="A429" s="6"/>
+      <c r="A429" s="3"/>
       <c r="B429" s="4"/>
     </row>
     <row r="430">
-      <c r="A430" s="6"/>
+      <c r="A430" s="3"/>
       <c r="B430" s="4"/>
     </row>
     <row r="431">
-      <c r="A431" s="6"/>
+      <c r="A431" s="3"/>
       <c r="B431" s="4"/>
     </row>
     <row r="432">
-      <c r="A432" s="6"/>
+      <c r="A432" s="3"/>
       <c r="B432" s="4"/>
     </row>
     <row r="433">
-      <c r="A433" s="6"/>
+      <c r="A433" s="3"/>
       <c r="B433" s="4"/>
     </row>
     <row r="434">
-      <c r="A434" s="6"/>
+      <c r="A434" s="3"/>
       <c r="B434" s="4"/>
     </row>
     <row r="435">
-      <c r="A435" s="6"/>
+      <c r="A435" s="3"/>
       <c r="B435" s="4"/>
     </row>
     <row r="436">
-      <c r="A436" s="6"/>
+      <c r="A436" s="3"/>
       <c r="B436" s="4"/>
     </row>
     <row r="437">
-      <c r="A437" s="6"/>
+      <c r="A437" s="3"/>
       <c r="B437" s="4"/>
     </row>
     <row r="438">
-      <c r="A438" s="6"/>
+      <c r="A438" s="3"/>
       <c r="B438" s="4"/>
     </row>
     <row r="439">
-      <c r="A439" s="6"/>
+      <c r="A439" s="3"/>
       <c r="B439" s="4"/>
     </row>
     <row r="440">
-      <c r="A440" s="6"/>
+      <c r="A440" s="3"/>
       <c r="B440" s="4"/>
     </row>
     <row r="441">
-      <c r="A441" s="6"/>
+      <c r="A441" s="3"/>
       <c r="B441" s="4"/>
     </row>
     <row r="442">
-      <c r="A442" s="6"/>
+      <c r="A442" s="3"/>
       <c r="B442" s="4"/>
     </row>
     <row r="443">
-      <c r="A443" s="6"/>
+      <c r="A443" s="3"/>
       <c r="B443" s="4"/>
     </row>
     <row r="444">
-      <c r="A444" s="6"/>
+      <c r="A444" s="3"/>
       <c r="B444" s="4"/>
     </row>
     <row r="445">
-      <c r="A445" s="6"/>
+      <c r="A445" s="3"/>
       <c r="B445" s="4"/>
     </row>
     <row r="446">
-      <c r="A446" s="6"/>
+      <c r="A446" s="3"/>
       <c r="B446" s="4"/>
     </row>
     <row r="447">
-      <c r="A447" s="6"/>
+      <c r="A447" s="3"/>
       <c r="B447" s="4"/>
     </row>
     <row r="448">
-      <c r="A448" s="6"/>
+      <c r="A448" s="3"/>
       <c r="B448" s="4"/>
     </row>
     <row r="449">
-      <c r="A449" s="6"/>
+      <c r="A449" s="3"/>
       <c r="B449" s="4"/>
     </row>
     <row r="450">
-      <c r="A450" s="6"/>
+      <c r="A450" s="3"/>
       <c r="B450" s="4"/>
     </row>
     <row r="451">
-      <c r="A451" s="6"/>
+      <c r="A451" s="3"/>
       <c r="B451" s="4"/>
     </row>
     <row r="452">
-      <c r="A452" s="6"/>
+      <c r="A452" s="3"/>
       <c r="B452" s="4"/>
     </row>
     <row r="453">
-      <c r="A453" s="6"/>
+      <c r="A453" s="3"/>
       <c r="B453" s="4"/>
     </row>
     <row r="454">
-      <c r="A454" s="6"/>
+      <c r="A454" s="3"/>
       <c r="B454" s="4"/>
     </row>
     <row r="455">
-      <c r="A455" s="6"/>
+      <c r="A455" s="3"/>
       <c r="B455" s="4"/>
     </row>
     <row r="456">
-      <c r="A456" s="6"/>
+      <c r="A456" s="3"/>
       <c r="B456" s="4"/>
     </row>
     <row r="457">
-      <c r="A457" s="6"/>
+      <c r="A457" s="3"/>
       <c r="B457" s="4"/>
     </row>
     <row r="458">
-      <c r="A458" s="6"/>
+      <c r="A458" s="3"/>
       <c r="B458" s="4"/>
     </row>
     <row r="459">
-      <c r="A459" s="6"/>
+      <c r="A459" s="3"/>
       <c r="B459" s="4"/>
     </row>
     <row r="460">
-      <c r="A460" s="6"/>
+      <c r="A460" s="3"/>
       <c r="B460" s="4"/>
     </row>
     <row r="461">
-      <c r="A461" s="6"/>
+      <c r="A461" s="3"/>
       <c r="B461" s="4"/>
     </row>
     <row r="462">
-      <c r="A462" s="6"/>
+      <c r="A462" s="3"/>
       <c r="B462" s="4"/>
     </row>
     <row r="463">
-      <c r="A463" s="6"/>
+      <c r="A463" s="3"/>
       <c r="B463" s="4"/>
     </row>
     <row r="464">
-      <c r="A464" s="6"/>
+      <c r="A464" s="3"/>
       <c r="B464" s="4"/>
     </row>
     <row r="465">
-      <c r="A465" s="6"/>
+      <c r="A465" s="3"/>
       <c r="B465" s="4"/>
     </row>
     <row r="466">
-      <c r="A466" s="6"/>
+      <c r="A466" s="3"/>
       <c r="B466" s="4"/>
     </row>
     <row r="467">
-      <c r="A467" s="6"/>
+      <c r="A467" s="3"/>
       <c r="B467" s="4"/>
     </row>
     <row r="468">
-      <c r="A468" s="6"/>
+      <c r="A468" s="3"/>
       <c r="B468" s="4"/>
     </row>
     <row r="469">
-      <c r="A469" s="6"/>
+      <c r="A469" s="3"/>
       <c r="B469" s="4"/>
     </row>
     <row r="470">
-      <c r="A470" s="6"/>
+      <c r="A470" s="3"/>
       <c r="B470" s="4"/>
     </row>
     <row r="471">
-      <c r="A471" s="6"/>
+      <c r="A471" s="3"/>
       <c r="B471" s="4"/>
     </row>
     <row r="472">
-      <c r="A472" s="6"/>
+      <c r="A472" s="3"/>
       <c r="B472" s="4"/>
     </row>
     <row r="473">
-      <c r="A473" s="6"/>
+      <c r="A473" s="3"/>
       <c r="B473" s="4"/>
     </row>
     <row r="474">
-      <c r="A474" s="6"/>
+      <c r="A474" s="3"/>
       <c r="B474" s="4"/>
     </row>
     <row r="475">
-      <c r="A475" s="6"/>
+      <c r="A475" s="3"/>
       <c r="B475" s="4"/>
     </row>
     <row r="476">
-      <c r="A476" s="6"/>
+      <c r="A476" s="3"/>
       <c r="B476" s="4"/>
     </row>
     <row r="477">
-      <c r="A477" s="6"/>
+      <c r="A477" s="3"/>
       <c r="B477" s="4"/>
     </row>
     <row r="478">
-      <c r="A478" s="6"/>
+      <c r="A478" s="3"/>
       <c r="B478" s="4"/>
     </row>
     <row r="479">
-      <c r="A479" s="6"/>
+      <c r="A479" s="3"/>
       <c r="B479" s="4"/>
     </row>
     <row r="480">
-      <c r="A480" s="6"/>
+      <c r="A480" s="3"/>
       <c r="B480" s="4"/>
     </row>
     <row r="481">
-      <c r="A481" s="6"/>
+      <c r="A481" s="3"/>
       <c r="B481" s="4"/>
     </row>
     <row r="482">
-      <c r="A482" s="6"/>
+      <c r="A482" s="3"/>
       <c r="B482" s="4"/>
     </row>
     <row r="483">
-      <c r="A483" s="6"/>
+      <c r="A483" s="3"/>
       <c r="B483" s="4"/>
     </row>
     <row r="484">
-      <c r="A484" s="6"/>
+      <c r="A484" s="3"/>
       <c r="B484" s="4"/>
     </row>
     <row r="485">
-      <c r="A485" s="6"/>
+      <c r="A485" s="3"/>
       <c r="B485" s="4"/>
     </row>
     <row r="486">
-      <c r="A486" s="6"/>
+      <c r="A486" s="3"/>
       <c r="B486" s="4"/>
     </row>
     <row r="487">
-      <c r="A487" s="6"/>
+      <c r="A487" s="3"/>
       <c r="B487" s="4"/>
     </row>
     <row r="488">
-      <c r="A488" s="6"/>
+      <c r="A488" s="3"/>
       <c r="B488" s="4"/>
     </row>
     <row r="489">
-      <c r="A489" s="6"/>
+      <c r="A489" s="3"/>
       <c r="B489" s="4"/>
     </row>
     <row r="490">
-      <c r="A490" s="6"/>
+      <c r="A490" s="3"/>
       <c r="B490" s="4"/>
     </row>
     <row r="491">
-      <c r="A491" s="6"/>
+      <c r="A491" s="3"/>
       <c r="B491" s="4"/>
     </row>
     <row r="492">
-      <c r="A492" s="6"/>
+      <c r="A492" s="3"/>
       <c r="B492" s="4"/>
     </row>
     <row r="493">
-      <c r="A493" s="6"/>
+      <c r="A493" s="3"/>
       <c r="B493" s="4"/>
     </row>
     <row r="494">
-      <c r="A494" s="6"/>
+      <c r="A494" s="3"/>
       <c r="B494" s="4"/>
     </row>
     <row r="495">
-      <c r="A495" s="6"/>
+      <c r="A495" s="3"/>
       <c r="B495" s="4"/>
     </row>
     <row r="496">
-      <c r="A496" s="6"/>
+      <c r="A496" s="3"/>
       <c r="B496" s="4"/>
     </row>
     <row r="497">
-      <c r="A497" s="6"/>
+      <c r="A497" s="3"/>
       <c r="B497" s="4"/>
     </row>
     <row r="498">
-      <c r="A498" s="6"/>
+      <c r="A498" s="3"/>
       <c r="B498" s="4"/>
     </row>
     <row r="499">
-      <c r="A499" s="6"/>
+      <c r="A499" s="3"/>
       <c r="B499" s="4"/>
     </row>
     <row r="500">
-      <c r="A500" s="6"/>
+      <c r="A500" s="3"/>
       <c r="B500" s="4"/>
     </row>
     <row r="501">
-      <c r="A501" s="6"/>
+      <c r="A501" s="3"/>
       <c r="B501" s="4"/>
     </row>
     <row r="502">
-      <c r="A502" s="6"/>
+      <c r="A502" s="3"/>
       <c r="B502" s="4"/>
     </row>
     <row r="503">
-      <c r="A503" s="6"/>
+      <c r="A503" s="3"/>
       <c r="B503" s="4"/>
     </row>
     <row r="504">
-      <c r="A504" s="6"/>
+      <c r="A504" s="3"/>
       <c r="B504" s="4"/>
     </row>
     <row r="505">
-      <c r="A505" s="6"/>
+      <c r="A505" s="3"/>
       <c r="B505" s="4"/>
     </row>
     <row r="506">
-      <c r="A506" s="6"/>
+      <c r="A506" s="3"/>
       <c r="B506" s="4"/>
     </row>
     <row r="507">
-      <c r="A507" s="6"/>
+      <c r="A507" s="3"/>
       <c r="B507" s="4"/>
     </row>
     <row r="508">
-      <c r="A508" s="6"/>
+      <c r="A508" s="3"/>
       <c r="B508" s="4"/>
     </row>
     <row r="509">
-      <c r="A509" s="6"/>
+      <c r="A509" s="3"/>
       <c r="B509" s="4"/>
     </row>
     <row r="510">
-      <c r="A510" s="6"/>
+      <c r="A510" s="3"/>
       <c r="B510" s="4"/>
     </row>
     <row r="511">
-      <c r="A511" s="6"/>
+      <c r="A511" s="3"/>
       <c r="B511" s="4"/>
     </row>
     <row r="512">
-      <c r="A512" s="6"/>
+      <c r="A512" s="3"/>
       <c r="B512" s="4"/>
     </row>
     <row r="513">
-      <c r="A513" s="6"/>
+      <c r="A513" s="3"/>
       <c r="B513" s="4"/>
     </row>
     <row r="514">
-      <c r="A514" s="6"/>
+      <c r="A514" s="3"/>
       <c r="B514" s="4"/>
     </row>
     <row r="515">
-      <c r="A515" s="6"/>
+      <c r="A515" s="3"/>
       <c r="B515" s="4"/>
     </row>
     <row r="516">
-      <c r="A516" s="6"/>
+      <c r="A516" s="3"/>
       <c r="B516" s="4"/>
     </row>
     <row r="517">
-      <c r="A517" s="6"/>
+      <c r="A517" s="3"/>
       <c r="B517" s="4"/>
     </row>
     <row r="518">
-      <c r="A518" s="6"/>
+      <c r="A518" s="3"/>
       <c r="B518" s="4"/>
     </row>
     <row r="519">
-      <c r="A519" s="6"/>
+      <c r="A519" s="3"/>
       <c r="B519" s="4"/>
     </row>
     <row r="520">
-      <c r="A520" s="6"/>
+      <c r="A520" s="3"/>
       <c r="B520" s="4"/>
     </row>
     <row r="521">
-      <c r="A521" s="6"/>
+      <c r="A521" s="3"/>
       <c r="B521" s="4"/>
     </row>
     <row r="522">
-      <c r="A522" s="6"/>
+      <c r="A522" s="3"/>
       <c r="B522" s="4"/>
     </row>
     <row r="523">
-      <c r="A523" s="6"/>
+      <c r="A523" s="3"/>
       <c r="B523" s="4"/>
     </row>
     <row r="524">
-      <c r="A524" s="6"/>
+      <c r="A524" s="3"/>
       <c r="B524" s="4"/>
     </row>
     <row r="525">
-      <c r="A525" s="6"/>
+      <c r="A525" s="3"/>
       <c r="B525" s="4"/>
     </row>
     <row r="526">
-      <c r="A526" s="6"/>
+      <c r="A526" s="3"/>
       <c r="B526" s="4"/>
     </row>
     <row r="527">
-      <c r="A527" s="6"/>
+      <c r="A527" s="3"/>
       <c r="B527" s="4"/>
     </row>
     <row r="528">
-      <c r="A528" s="6"/>
+      <c r="A528" s="3"/>
       <c r="B528" s="4"/>
     </row>
     <row r="529">
-      <c r="A529" s="6"/>
+      <c r="A529" s="3"/>
       <c r="B529" s="4"/>
     </row>
     <row r="530">
-      <c r="A530" s="6"/>
+      <c r="A530" s="3"/>
       <c r="B530" s="4"/>
     </row>
     <row r="531">
-      <c r="A531" s="6"/>
+      <c r="A531" s="3"/>
       <c r="B531" s="4"/>
     </row>
     <row r="532">
-      <c r="A532" s="6"/>
+      <c r="A532" s="3"/>
       <c r="B532" s="4"/>
     </row>
     <row r="533">
-      <c r="A533" s="6"/>
+      <c r="A533" s="3"/>
       <c r="B533" s="4"/>
     </row>
     <row r="534">
-      <c r="A534" s="6"/>
+      <c r="A534" s="3"/>
       <c r="B534" s="4"/>
     </row>
     <row r="535">
-      <c r="A535" s="6"/>
+      <c r="A535" s="3"/>
       <c r="B535" s="4"/>
     </row>
     <row r="536">
-      <c r="A536" s="6"/>
+      <c r="A536" s="3"/>
       <c r="B536" s="4"/>
     </row>
     <row r="537">
-      <c r="A537" s="6"/>
+      <c r="A537" s="3"/>
       <c r="B537" s="4"/>
     </row>
     <row r="538">
-      <c r="A538" s="6"/>
+      <c r="A538" s="3"/>
       <c r="B538" s="4"/>
     </row>
     <row r="539">
-      <c r="A539" s="6"/>
+      <c r="A539" s="3"/>
       <c r="B539" s="4"/>
     </row>
     <row r="540">
-      <c r="A540" s="6"/>
+      <c r="A540" s="3"/>
       <c r="B540" s="4"/>
     </row>
     <row r="541">
-      <c r="A541" s="6"/>
+      <c r="A541" s="3"/>
       <c r="B541" s="4"/>
     </row>
     <row r="542">
-      <c r="A542" s="6"/>
+      <c r="A542" s="3"/>
       <c r="B542" s="4"/>
     </row>
     <row r="543">
-      <c r="A543" s="6"/>
+      <c r="A543" s="3"/>
       <c r="B543" s="4"/>
     </row>
     <row r="544">
-      <c r="A544" s="6"/>
+      <c r="A544" s="3"/>
       <c r="B544" s="4"/>
     </row>
     <row r="545">
-      <c r="A545" s="6"/>
+      <c r="A545" s="3"/>
       <c r="B545" s="4"/>
     </row>
     <row r="546">
-      <c r="A546" s="6"/>
+      <c r="A546" s="3"/>
       <c r="B546" s="4"/>
     </row>
     <row r="547">
-      <c r="A547" s="6"/>
+      <c r="A547" s="3"/>
       <c r="B547" s="4"/>
     </row>
     <row r="548">
-      <c r="A548" s="6"/>
+      <c r="A548" s="3"/>
       <c r="B548" s="4"/>
     </row>
     <row r="549">
-      <c r="A549" s="6"/>
+      <c r="A549" s="3"/>
       <c r="B549" s="4"/>
     </row>
     <row r="550">
-      <c r="A550" s="6"/>
+      <c r="A550" s="3"/>
       <c r="B550" s="4"/>
     </row>
     <row r="551">
-      <c r="A551" s="6"/>
+      <c r="A551" s="3"/>
       <c r="B551" s="4"/>
     </row>
     <row r="552">
-      <c r="A552" s="6"/>
+      <c r="A552" s="3"/>
       <c r="B552" s="4"/>
     </row>
     <row r="553">
-      <c r="A553" s="6"/>
+      <c r="A553" s="3"/>
       <c r="B553" s="4"/>
     </row>
     <row r="554">
-      <c r="A554" s="6"/>
+      <c r="A554" s="3"/>
       <c r="B554" s="4"/>
     </row>
     <row r="555">
-      <c r="A555" s="6"/>
+      <c r="A555" s="3"/>
       <c r="B555" s="4"/>
     </row>
     <row r="556">
-      <c r="A556" s="6"/>
+      <c r="A556" s="3"/>
       <c r="B556" s="4"/>
     </row>
     <row r="557">
-      <c r="A557" s="6"/>
+      <c r="A557" s="3"/>
       <c r="B557" s="4"/>
     </row>
     <row r="558">
-      <c r="A558" s="6"/>
+      <c r="A558" s="3"/>
       <c r="B558" s="4"/>
     </row>
     <row r="559">
-      <c r="A559" s="6"/>
+      <c r="A559" s="3"/>
       <c r="B559" s="4"/>
     </row>
     <row r="560">
-      <c r="A560" s="6"/>
+      <c r="A560" s="3"/>
       <c r="B560" s="4"/>
     </row>
     <row r="561">
-      <c r="A561" s="6"/>
+      <c r="A561" s="3"/>
       <c r="B561" s="4"/>
     </row>
     <row r="562">
-      <c r="A562" s="6"/>
+      <c r="A562" s="3"/>
       <c r="B562" s="4"/>
     </row>
     <row r="563">
-      <c r="A563" s="6"/>
+      <c r="A563" s="3"/>
       <c r="B563" s="4"/>
     </row>
     <row r="564">
-      <c r="A564" s="6"/>
+      <c r="A564" s="3"/>
       <c r="B564" s="4"/>
     </row>
     <row r="565">
-      <c r="A565" s="6"/>
+      <c r="A565" s="3"/>
       <c r="B565" s="4"/>
     </row>
     <row r="566">
-      <c r="A566" s="6"/>
+      <c r="A566" s="3"/>
       <c r="B566" s="4"/>
     </row>
     <row r="567">
-      <c r="A567" s="6"/>
+      <c r="A567" s="3"/>
       <c r="B567" s="4"/>
     </row>
     <row r="568">
-      <c r="A568" s="6"/>
+      <c r="A568" s="3"/>
       <c r="B568" s="4"/>
     </row>
     <row r="569">
-      <c r="A569" s="6"/>
+      <c r="A569" s="3"/>
       <c r="B569" s="4"/>
     </row>
     <row r="570">
-      <c r="A570" s="6"/>
+      <c r="A570" s="3"/>
       <c r="B570" s="4"/>
     </row>
     <row r="571">
-      <c r="A571" s="6"/>
+      <c r="A571" s="3"/>
       <c r="B571" s="4"/>
     </row>
     <row r="572">
-      <c r="A572" s="6"/>
+      <c r="A572" s="3"/>
       <c r="B572" s="4"/>
     </row>
     <row r="573">
-      <c r="A573" s="6"/>
+      <c r="A573" s="3"/>
       <c r="B573" s="4"/>
     </row>
     <row r="574">
-      <c r="A574" s="6"/>
+      <c r="A574" s="3"/>
       <c r="B574" s="4"/>
     </row>
     <row r="575">
-      <c r="A575" s="6"/>
+      <c r="A575" s="3"/>
       <c r="B575" s="4"/>
     </row>
     <row r="576">
-      <c r="A576" s="6"/>
+      <c r="A576" s="3"/>
       <c r="B576" s="4"/>
     </row>
     <row r="577">
-      <c r="A577" s="6"/>
+      <c r="A577" s="3"/>
       <c r="B577" s="4"/>
     </row>
     <row r="578">
-      <c r="A578" s="6"/>
+      <c r="A578" s="3"/>
       <c r="B578" s="4"/>
     </row>
     <row r="579">
-      <c r="A579" s="6"/>
+      <c r="A579" s="3"/>
       <c r="B579" s="4"/>
     </row>
     <row r="580">
-      <c r="A580" s="6"/>
+      <c r="A580" s="3"/>
       <c r="B580" s="4"/>
     </row>
     <row r="581">
-      <c r="A581" s="6"/>
+      <c r="A581" s="3"/>
       <c r="B581" s="4"/>
     </row>
     <row r="582">
-      <c r="A582" s="6"/>
+      <c r="A582" s="3"/>
       <c r="B582" s="4"/>
     </row>
     <row r="583">
-      <c r="A583" s="6"/>
+      <c r="A583" s="3"/>
       <c r="B583" s="4"/>
     </row>
     <row r="584">
-      <c r="A584" s="6"/>
+      <c r="A584" s="3"/>
       <c r="B584" s="4"/>
     </row>
     <row r="585">
-      <c r="A585" s="6"/>
+      <c r="A585" s="3"/>
       <c r="B585" s="4"/>
     </row>
     <row r="586">
-      <c r="A586" s="6"/>
+      <c r="A586" s="3"/>
       <c r="B586" s="4"/>
     </row>
     <row r="587">
-      <c r="A587" s="6"/>
+      <c r="A587" s="3"/>
       <c r="B587" s="4"/>
     </row>
     <row r="588">
-      <c r="A588" s="6"/>
+      <c r="A588" s="3"/>
       <c r="B588" s="4"/>
     </row>
     <row r="589">
-      <c r="A589" s="6"/>
+      <c r="A589" s="3"/>
       <c r="B589" s="4"/>
     </row>
     <row r="590">
-      <c r="A590" s="6"/>
+      <c r="A590" s="3"/>
       <c r="B590" s="4"/>
     </row>
     <row r="591">
-      <c r="A591" s="6"/>
+      <c r="A591" s="3"/>
       <c r="B591" s="4"/>
     </row>
     <row r="592">
-      <c r="A592" s="6"/>
+      <c r="A592" s="3"/>
       <c r="B592" s="4"/>
     </row>
     <row r="593">
-      <c r="A593" s="6"/>
+      <c r="A593" s="3"/>
       <c r="B593" s="4"/>
     </row>
     <row r="594">
-      <c r="A594" s="6"/>
+      <c r="A594" s="3"/>
       <c r="B594" s="4"/>
     </row>
     <row r="595">
-      <c r="A595" s="6"/>
+      <c r="A595" s="3"/>
       <c r="B595" s="4"/>
     </row>
     <row r="596">
-      <c r="A596" s="6"/>
+      <c r="A596" s="3"/>
       <c r="B596" s="4"/>
     </row>
     <row r="597">
-      <c r="A597" s="6"/>
+      <c r="A597" s="3"/>
       <c r="B597" s="4"/>
     </row>
     <row r="598">
-      <c r="A598" s="6"/>
+      <c r="A598" s="3"/>
       <c r="B598" s="4"/>
     </row>
     <row r="599">
-      <c r="A599" s="6"/>
+      <c r="A599" s="3"/>
       <c r="B599" s="4"/>
     </row>
     <row r="600">
-      <c r="A600" s="6"/>
+      <c r="A600" s="3"/>
       <c r="B600" s="4"/>
     </row>
     <row r="601">
-      <c r="A601" s="6"/>
+      <c r="A601" s="3"/>
       <c r="B601" s="4"/>
     </row>
     <row r="602">
-      <c r="A602" s="6"/>
+      <c r="A602" s="3"/>
       <c r="B602" s="4"/>
     </row>
     <row r="603">
-      <c r="A603" s="6"/>
+      <c r="A603" s="3"/>
       <c r="B603" s="4"/>
     </row>
     <row r="604">
-      <c r="A604" s="6"/>
+      <c r="A604" s="3"/>
       <c r="B604" s="4"/>
     </row>
     <row r="605">
-      <c r="A605" s="6"/>
+      <c r="A605" s="3"/>
       <c r="B605" s="4"/>
     </row>
     <row r="606">
-      <c r="A606" s="6"/>
+      <c r="A606" s="3"/>
       <c r="B606" s="4"/>
     </row>
     <row r="607">
-      <c r="A607" s="6"/>
+      <c r="A607" s="3"/>
       <c r="B607" s="4"/>
     </row>
     <row r="608">
-      <c r="A608" s="6"/>
+      <c r="A608" s="3"/>
       <c r="B608" s="4"/>
     </row>
     <row r="609">
-      <c r="A609" s="6"/>
+      <c r="A609" s="3"/>
       <c r="B609" s="4"/>
     </row>
     <row r="610">
-      <c r="A610" s="6"/>
+      <c r="A610" s="3"/>
       <c r="B610" s="4"/>
     </row>
     <row r="611">
-      <c r="A611" s="6"/>
+      <c r="A611" s="3"/>
       <c r="B611" s="4"/>
     </row>
     <row r="612">
-      <c r="A612" s="6"/>
+      <c r="A612" s="3"/>
       <c r="B612" s="4"/>
     </row>
     <row r="613">
-      <c r="A613" s="6"/>
+      <c r="A613" s="3"/>
       <c r="B613" s="4"/>
     </row>
     <row r="614">
-      <c r="A614" s="6"/>
+      <c r="A614" s="3"/>
       <c r="B614" s="4"/>
     </row>
     <row r="615">
-      <c r="A615" s="6"/>
+      <c r="A615" s="3"/>
       <c r="B615" s="4"/>
     </row>
     <row r="616">
-      <c r="A616" s="6"/>
+      <c r="A616" s="3"/>
       <c r="B616" s="4"/>
     </row>
     <row r="617">
-      <c r="A617" s="6"/>
+      <c r="A617" s="3"/>
       <c r="B617" s="4"/>
     </row>
     <row r="618">
-      <c r="A618" s="6"/>
+      <c r="A618" s="3"/>
       <c r="B618" s="4"/>
     </row>
     <row r="619">
-      <c r="A619" s="6"/>
+      <c r="A619" s="3"/>
       <c r="B619" s="4"/>
     </row>
     <row r="620">
-      <c r="A620" s="6"/>
+      <c r="A620" s="3"/>
       <c r="B620" s="4"/>
     </row>
     <row r="621">
-      <c r="A621" s="6"/>
+      <c r="A621" s="3"/>
       <c r="B621" s="4"/>
     </row>
     <row r="622">
-      <c r="A622" s="6"/>
+      <c r="A622" s="3"/>
       <c r="B622" s="4"/>
     </row>
     <row r="623">
-      <c r="A623" s="6"/>
+      <c r="A623" s="3"/>
       <c r="B623" s="4"/>
     </row>
     <row r="624">
-      <c r="A624" s="6"/>
+      <c r="A624" s="3"/>
       <c r="B624" s="4"/>
     </row>
     <row r="625">
-      <c r="A625" s="6"/>
+      <c r="A625" s="3"/>
       <c r="B625" s="4"/>
     </row>
     <row r="626">
-      <c r="A626" s="6"/>
+      <c r="A626" s="3"/>
       <c r="B626" s="4"/>
     </row>
     <row r="627">
-      <c r="A627" s="6"/>
+      <c r="A627" s="3"/>
       <c r="B627" s="4"/>
     </row>
     <row r="628">
-      <c r="A628" s="6"/>
+      <c r="A628" s="3"/>
       <c r="B628" s="4"/>
     </row>
     <row r="629">
-      <c r="A629" s="6"/>
+      <c r="A629" s="3"/>
       <c r="B629" s="4"/>
     </row>
     <row r="630">
-      <c r="A630" s="6"/>
+      <c r="A630" s="3"/>
       <c r="B630" s="4"/>
     </row>
     <row r="631">
-      <c r="A631" s="6"/>
+      <c r="A631" s="3"/>
       <c r="B631" s="4"/>
     </row>
     <row r="632">
-      <c r="A632" s="6"/>
+      <c r="A632" s="3"/>
       <c r="B632" s="4"/>
     </row>
     <row r="633">
-      <c r="A633" s="6"/>
+      <c r="A633" s="3"/>
       <c r="B633" s="4"/>
     </row>
     <row r="634">
-      <c r="A634" s="6"/>
+      <c r="A634" s="3"/>
       <c r="B634" s="4"/>
     </row>
     <row r="635">
-      <c r="A635" s="6"/>
+      <c r="A635" s="3"/>
       <c r="B635" s="4"/>
     </row>
     <row r="636">
-      <c r="A636" s="6"/>
+      <c r="A636" s="3"/>
       <c r="B636" s="4"/>
     </row>
     <row r="637">
-      <c r="A637" s="6"/>
+      <c r="A637" s="3"/>
       <c r="B637" s="4"/>
     </row>
     <row r="638">
-      <c r="A638" s="6"/>
+      <c r="A638" s="3"/>
       <c r="B638" s="4"/>
     </row>
     <row r="639">
-      <c r="A639" s="7"/>
+      <c r="A639" s="3"/>
+      <c r="B639" s="4"/>
     </row>
     <row r="640">
-      <c r="A640" s="7"/>
+      <c r="A640" s="3"/>
+      <c r="B640" s="4"/>
     </row>
     <row r="641">
-      <c r="A641" s="7"/>
+      <c r="A641" s="3"/>
+      <c r="B641" s="4"/>
     </row>
     <row r="642">
-      <c r="A642" s="7"/>
+      <c r="A642" s="3"/>
+      <c r="B642" s="4"/>
     </row>
     <row r="643">
-      <c r="A643" s="7"/>
+      <c r="A643" s="3"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644">
-      <c r="A644" s="7"/>
+      <c r="A644" s="3"/>
+      <c r="B644" s="4"/>
     </row>
     <row r="645">
-      <c r="A645" s="7"/>
+      <c r="A645" s="3"/>
+      <c r="B645" s="4"/>
     </row>
     <row r="646">
-      <c r="A646" s="7"/>
+      <c r="A646" s="3"/>
+      <c r="B646" s="4"/>
     </row>
     <row r="647">
-      <c r="A647" s="7"/>
+      <c r="A647" s="3"/>
+      <c r="B647" s="4"/>
     </row>
     <row r="648">
-      <c r="A648" s="7"/>
+      <c r="A648" s="3"/>
+      <c r="B648" s="4"/>
     </row>
     <row r="649">
-      <c r="A649" s="7"/>
+      <c r="A649" s="3"/>
+      <c r="B649" s="4"/>
     </row>
     <row r="650">
-      <c r="A650" s="7"/>
+      <c r="A650" s="3"/>
+      <c r="B650" s="4"/>
     </row>
     <row r="651">
-      <c r="A651" s="7"/>
+      <c r="A651" s="3"/>
+      <c r="B651" s="4"/>
     </row>
     <row r="652">
-      <c r="A652" s="7"/>
+      <c r="A652" s="3"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="653">
-      <c r="A653" s="7"/>
+      <c r="A653" s="3"/>
+      <c r="B653" s="4"/>
     </row>
     <row r="654">
-      <c r="A654" s="7"/>
+      <c r="A654" s="3"/>
+      <c r="B654" s="4"/>
     </row>
     <row r="655">
-      <c r="A655" s="7"/>
+      <c r="A655" s="3"/>
+      <c r="B655" s="4"/>
     </row>
     <row r="656">
-      <c r="A656" s="7"/>
+      <c r="A656" s="3"/>
+      <c r="B656" s="4"/>
     </row>
     <row r="657">
-      <c r="A657" s="7"/>
+      <c r="A657" s="3"/>
+      <c r="B657" s="4"/>
     </row>
     <row r="658">
-      <c r="A658" s="7"/>
+      <c r="A658" s="3"/>
+      <c r="B658" s="4"/>
     </row>
     <row r="659">
-      <c r="A659" s="7"/>
+      <c r="A659" s="3"/>
+      <c r="B659" s="4"/>
     </row>
     <row r="660">
-      <c r="A660" s="7"/>
+      <c r="A660" s="3"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="661">
-      <c r="A661" s="7"/>
+      <c r="A661" s="3"/>
+      <c r="B661" s="4"/>
     </row>
     <row r="662">
-      <c r="A662" s="7"/>
+      <c r="A662" s="3"/>
+      <c r="B662" s="4"/>
     </row>
     <row r="663">
-      <c r="A663" s="7"/>
+      <c r="A663" s="3"/>
+      <c r="B663" s="4"/>
     </row>
     <row r="664">
-      <c r="A664" s="7"/>
+      <c r="A664" s="3"/>
+      <c r="B664" s="4"/>
     </row>
     <row r="665">
-      <c r="A665" s="7"/>
+      <c r="A665" s="3"/>
+      <c r="B665" s="4"/>
     </row>
     <row r="666">
-      <c r="A666" s="7"/>
+      <c r="A666" s="3"/>
+      <c r="B666" s="4"/>
     </row>
     <row r="667">
-      <c r="A667" s="7"/>
+      <c r="A667" s="3"/>
+      <c r="B667" s="4"/>
     </row>
     <row r="668">
-      <c r="A668" s="7"/>
+      <c r="A668" s="3"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="669">
-      <c r="A669" s="7"/>
+      <c r="A669" s="3"/>
+      <c r="B669" s="4"/>
     </row>
     <row r="670">
-      <c r="A670" s="7"/>
+      <c r="A670" s="3"/>
+      <c r="B670" s="4"/>
     </row>
     <row r="671">
-      <c r="A671" s="7"/>
+      <c r="A671" s="3"/>
+      <c r="B671" s="4"/>
     </row>
     <row r="672">
-      <c r="A672" s="7"/>
+      <c r="A672" s="3"/>
+      <c r="B672" s="4"/>
     </row>
     <row r="673">
-      <c r="A673" s="7"/>
+      <c r="A673" s="3"/>
+      <c r="B673" s="4"/>
     </row>
     <row r="674">
-      <c r="A674" s="7"/>
+      <c r="A674" s="3"/>
+      <c r="B674" s="4"/>
     </row>
     <row r="675">
-      <c r="A675" s="7"/>
+      <c r="A675" s="3"/>
+      <c r="B675" s="4"/>
     </row>
     <row r="676">
-      <c r="A676" s="7"/>
+      <c r="A676" s="3"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="677">
-      <c r="A677" s="7"/>
+      <c r="A677" s="3"/>
+      <c r="B677" s="4"/>
     </row>
     <row r="678">
-      <c r="A678" s="7"/>
+      <c r="A678" s="3"/>
+      <c r="B678" s="4"/>
     </row>
     <row r="679">
-      <c r="A679" s="7"/>
+      <c r="A679" s="3"/>
+      <c r="B679" s="4"/>
     </row>
     <row r="680">
-      <c r="A680" s="7"/>
+      <c r="A680" s="3"/>
+      <c r="B680" s="4"/>
     </row>
     <row r="681">
-      <c r="A681" s="7"/>
+      <c r="A681" s="3"/>
+      <c r="B681" s="4"/>
     </row>
     <row r="682">
-      <c r="A682" s="7"/>
+      <c r="A682" s="3"/>
+      <c r="B682" s="4"/>
     </row>
     <row r="683">
-      <c r="A683" s="7"/>
+      <c r="A683" s="3"/>
+      <c r="B683" s="4"/>
     </row>
     <row r="684">
-      <c r="A684" s="7"/>
+      <c r="A684" s="3"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="685">
-      <c r="A685" s="7"/>
+      <c r="A685" s="3"/>
+      <c r="B685" s="4"/>
     </row>
     <row r="686">
-      <c r="A686" s="7"/>
+      <c r="A686" s="3"/>
+      <c r="B686" s="4"/>
     </row>
     <row r="687">
-      <c r="A687" s="7"/>
+      <c r="A687" s="3"/>
+      <c r="B687" s="4"/>
     </row>
     <row r="688">
-      <c r="A688" s="7"/>
+      <c r="A688" s="3"/>
+      <c r="B688" s="4"/>
     </row>
     <row r="689">
-      <c r="A689" s="7"/>
+      <c r="A689" s="3"/>
+      <c r="B689" s="4"/>
     </row>
     <row r="690">
-      <c r="A690" s="7"/>
+      <c r="A690" s="3"/>
+      <c r="B690" s="4"/>
     </row>
     <row r="691">
-      <c r="A691" s="7"/>
+      <c r="A691" s="3"/>
+      <c r="B691" s="4"/>
     </row>
     <row r="692">
-      <c r="A692" s="7"/>
+      <c r="A692" s="3"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="693">
-      <c r="A693" s="7"/>
+      <c r="A693" s="3"/>
+      <c r="B693" s="4"/>
     </row>
     <row r="694">
-      <c r="A694" s="7"/>
+      <c r="A694" s="3"/>
+      <c r="B694" s="4"/>
     </row>
     <row r="695">
-      <c r="A695" s="7"/>
+      <c r="A695" s="3"/>
+      <c r="B695" s="4"/>
     </row>
     <row r="696">
-      <c r="A696" s="7"/>
+      <c r="A696" s="3"/>
+      <c r="B696" s="4"/>
     </row>
     <row r="697">
-      <c r="A697" s="7"/>
+      <c r="A697" s="3"/>
+      <c r="B697" s="4"/>
     </row>
     <row r="698">
-      <c r="A698" s="7"/>
+      <c r="A698" s="3"/>
+      <c r="B698" s="4"/>
     </row>
     <row r="699">
-      <c r="A699" s="7"/>
+      <c r="A699" s="3"/>
+      <c r="B699" s="4"/>
     </row>
     <row r="700">
-      <c r="A700" s="7"/>
+      <c r="A700" s="3"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="701">
-      <c r="A701" s="7"/>
+      <c r="A701" s="3"/>
+      <c r="B701" s="4"/>
     </row>
     <row r="702">
-      <c r="A702" s="7"/>
+      <c r="A702" s="3"/>
+      <c r="B702" s="4"/>
     </row>
     <row r="703">
-      <c r="A703" s="7"/>
+      <c r="A703" s="3"/>
+      <c r="B703" s="4"/>
     </row>
     <row r="704">
-      <c r="A704" s="7"/>
+      <c r="A704" s="3"/>
+      <c r="B704" s="4"/>
     </row>
     <row r="705">
-      <c r="A705" s="7"/>
+      <c r="A705" s="3"/>
+      <c r="B705" s="4"/>
     </row>
     <row r="706">
-      <c r="A706" s="7"/>
+      <c r="A706" s="3"/>
+      <c r="B706" s="4"/>
     </row>
     <row r="707">
-      <c r="A707" s="7"/>
+      <c r="A707" s="3"/>
+      <c r="B707" s="4"/>
     </row>
     <row r="708">
-      <c r="A708" s="7"/>
+      <c r="A708" s="3"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709">
-      <c r="A709" s="7"/>
+      <c r="A709" s="3"/>
+      <c r="B709" s="4"/>
     </row>
     <row r="710">
-      <c r="A710" s="7"/>
+      <c r="A710" s="3"/>
+      <c r="B710" s="4"/>
     </row>
     <row r="711">
-      <c r="A711" s="7"/>
+      <c r="A711" s="3"/>
+      <c r="B711" s="4"/>
     </row>
     <row r="712">
-      <c r="A712" s="7"/>
+      <c r="A712" s="3"/>
+      <c r="B712" s="4"/>
     </row>
     <row r="713">
-      <c r="A713" s="7"/>
+      <c r="A713" s="3"/>
+      <c r="B713" s="4"/>
     </row>
     <row r="714">
-      <c r="A714" s="7"/>
+      <c r="A714" s="3"/>
+      <c r="B714" s="4"/>
     </row>
     <row r="715">
-      <c r="A715" s="7"/>
+      <c r="A715" s="3"/>
+      <c r="B715" s="4"/>
     </row>
     <row r="716">
-      <c r="A716" s="7"/>
+      <c r="A716" s="3"/>
+      <c r="B716" s="4"/>
     </row>
     <row r="717">
-      <c r="A717" s="7"/>
+      <c r="A717" s="3"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="718">
-      <c r="A718" s="7"/>
+      <c r="A718" s="3"/>
+      <c r="B718" s="4"/>
     </row>
     <row r="719">
-      <c r="A719" s="7"/>
+      <c r="A719" s="3"/>
+      <c r="B719" s="4"/>
     </row>
     <row r="720">
-      <c r="A720" s="7"/>
+      <c r="A720" s="3"/>
+      <c r="B720" s="4"/>
     </row>
     <row r="721">
-      <c r="A721" s="7"/>
+      <c r="A721" s="3"/>
+      <c r="B721" s="4"/>
     </row>
     <row r="722">
-      <c r="A722" s="7"/>
+      <c r="A722" s="3"/>
+      <c r="B722" s="4"/>
     </row>
     <row r="723">
-      <c r="A723" s="7"/>
+      <c r="A723" s="3"/>
+      <c r="B723" s="4"/>
     </row>
     <row r="724">
-      <c r="A724" s="7"/>
+      <c r="A724" s="3"/>
+      <c r="B724" s="4"/>
     </row>
     <row r="725">
-      <c r="A725" s="7"/>
+      <c r="A725" s="3"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="726">
-      <c r="A726" s="7"/>
+      <c r="A726" s="3"/>
+      <c r="B726" s="4"/>
     </row>
     <row r="727">
-      <c r="A727" s="7"/>
+      <c r="A727" s="3"/>
+      <c r="B727" s="4"/>
     </row>
     <row r="728">
-      <c r="A728" s="7"/>
+      <c r="A728" s="3"/>
+      <c r="B728" s="4"/>
     </row>
     <row r="729">
-      <c r="A729" s="7"/>
+      <c r="A729" s="3"/>
+      <c r="B729" s="4"/>
     </row>
     <row r="730">
-      <c r="A730" s="7"/>
+      <c r="A730" s="3"/>
+      <c r="B730" s="4"/>
     </row>
     <row r="731">
-      <c r="A731" s="7"/>
+      <c r="A731" s="3"/>
+      <c r="B731" s="4"/>
     </row>
     <row r="732">
-      <c r="A732" s="7"/>
+      <c r="A732" s="5"/>
     </row>
     <row r="733">
-      <c r="A733" s="7"/>
+      <c r="A733" s="5"/>
     </row>
     <row r="734">
-      <c r="A734" s="7"/>
+      <c r="A734" s="5"/>
     </row>
     <row r="735">
-      <c r="A735" s="7"/>
+      <c r="A735" s="5"/>
     </row>
     <row r="736">
-      <c r="A736" s="7"/>
+      <c r="A736" s="5"/>
     </row>
     <row r="737">
-      <c r="A737" s="7"/>
+      <c r="A737" s="5"/>
     </row>
     <row r="738">
-      <c r="A738" s="7"/>
+      <c r="A738" s="5"/>
     </row>
     <row r="739">
-      <c r="A739" s="7"/>
+      <c r="A739" s="5"/>
     </row>
     <row r="740">
-      <c r="A740" s="7"/>
+      <c r="A740" s="5"/>
     </row>
     <row r="741">
-      <c r="A741" s="7"/>
+      <c r="A741" s="5"/>
     </row>
     <row r="742">
-      <c r="A742" s="7"/>
+      <c r="A742" s="5"/>
     </row>
     <row r="743">
-      <c r="A743" s="7"/>
+      <c r="A743" s="5"/>
     </row>
     <row r="744">
-      <c r="A744" s="7"/>
+      <c r="A744" s="5"/>
     </row>
     <row r="745">
-      <c r="A745" s="7"/>
+      <c r="A745" s="5"/>
     </row>
     <row r="746">
-      <c r="A746" s="7"/>
+      <c r="A746" s="5"/>
     </row>
     <row r="747">
-      <c r="A747" s="7"/>
+      <c r="A747" s="5"/>
     </row>
     <row r="748">
-      <c r="A748" s="7"/>
+      <c r="A748" s="5"/>
     </row>
     <row r="749">
-      <c r="A749" s="7"/>
+      <c r="A749" s="5"/>
     </row>
     <row r="750">
-      <c r="A750" s="7"/>
+      <c r="A750" s="5"/>
     </row>
     <row r="751">
-      <c r="A751" s="7"/>
+      <c r="A751" s="5"/>
     </row>
     <row r="752">
-      <c r="A752" s="7"/>
+      <c r="A752" s="5"/>
     </row>
     <row r="753">
-      <c r="A753" s="7"/>
+      <c r="A753" s="5"/>
     </row>
     <row r="754">
-      <c r="A754" s="7"/>
+      <c r="A754" s="5"/>
     </row>
     <row r="755">
-      <c r="A755" s="7"/>
+      <c r="A755" s="5"/>
     </row>
     <row r="756">
-      <c r="A756" s="7"/>
+      <c r="A756" s="5"/>
     </row>
     <row r="757">
-      <c r="A757" s="7"/>
+      <c r="A757" s="5"/>
     </row>
     <row r="758">
-      <c r="A758" s="7"/>
+      <c r="A758" s="5"/>
     </row>
     <row r="759">
-      <c r="A759" s="7"/>
+      <c r="A759" s="5"/>
     </row>
     <row r="760">
-      <c r="A760" s="7"/>
+      <c r="A760" s="5"/>
     </row>
     <row r="761">
-      <c r="A761" s="7"/>
+      <c r="A761" s="5"/>
     </row>
     <row r="762">
-      <c r="A762" s="7"/>
+      <c r="A762" s="5"/>
     </row>
     <row r="763">
-      <c r="A763" s="7"/>
+      <c r="A763" s="5"/>
     </row>
     <row r="764">
-      <c r="A764" s="7"/>
+      <c r="A764" s="5"/>
     </row>
     <row r="765">
-      <c r="A765" s="7"/>
+      <c r="A765" s="5"/>
     </row>
     <row r="766">
-      <c r="A766" s="7"/>
+      <c r="A766" s="5"/>
     </row>
     <row r="767">
-      <c r="A767" s="7"/>
+      <c r="A767" s="5"/>
     </row>
     <row r="768">
-      <c r="A768" s="7"/>
+      <c r="A768" s="5"/>
     </row>
     <row r="769">
-      <c r="A769" s="7"/>
+      <c r="A769" s="5"/>
     </row>
     <row r="770">
-      <c r="A770" s="7"/>
+      <c r="A770" s="5"/>
     </row>
     <row r="771">
-      <c r="A771" s="7"/>
+      <c r="A771" s="5"/>
     </row>
     <row r="772">
-      <c r="A772" s="7"/>
+      <c r="A772" s="5"/>
     </row>
     <row r="773">
-      <c r="A773" s="7"/>
+      <c r="A773" s="5"/>
     </row>
     <row r="774">
-      <c r="A774" s="7"/>
+      <c r="A774" s="5"/>
     </row>
     <row r="775">
-      <c r="A775" s="7"/>
+      <c r="A775" s="5"/>
     </row>
     <row r="776">
-      <c r="A776" s="7"/>
+      <c r="A776" s="5"/>
     </row>
     <row r="777">
-      <c r="A777" s="7"/>
+      <c r="A777" s="5"/>
     </row>
     <row r="778">
-      <c r="A778" s="7"/>
+      <c r="A778" s="5"/>
     </row>
     <row r="779">
-      <c r="A779" s="7"/>
+      <c r="A779" s="5"/>
     </row>
     <row r="780">
-      <c r="A780" s="7"/>
+      <c r="A780" s="5"/>
     </row>
     <row r="781">
-      <c r="A781" s="7"/>
+      <c r="A781" s="5"/>
     </row>
     <row r="782">
-      <c r="A782" s="7"/>
+      <c r="A782" s="5"/>
     </row>
     <row r="783">
-      <c r="A783" s="7"/>
+      <c r="A783" s="5"/>
     </row>
     <row r="784">
-      <c r="A784" s="7"/>
+      <c r="A784" s="5"/>
     </row>
     <row r="785">
-      <c r="A785" s="7"/>
+      <c r="A785" s="5"/>
     </row>
     <row r="786">
-      <c r="A786" s="7"/>
+      <c r="A786" s="5"/>
     </row>
     <row r="787">
-      <c r="A787" s="7"/>
+      <c r="A787" s="5"/>
     </row>
     <row r="788">
-      <c r="A788" s="7"/>
+      <c r="A788" s="5"/>
     </row>
     <row r="789">
-      <c r="A789" s="7"/>
+      <c r="A789" s="5"/>
     </row>
     <row r="790">
-      <c r="A790" s="7"/>
+      <c r="A790" s="5"/>
     </row>
     <row r="791">
-      <c r="A791" s="7"/>
+      <c r="A791" s="5"/>
     </row>
     <row r="792">
-      <c r="A792" s="7"/>
+      <c r="A792" s="5"/>
     </row>
     <row r="793">
-      <c r="A793" s="7"/>
+      <c r="A793" s="5"/>
     </row>
     <row r="794">
-      <c r="A794" s="7"/>
+      <c r="A794" s="5"/>
     </row>
     <row r="795">
-      <c r="A795" s="7"/>
+      <c r="A795" s="5"/>
     </row>
     <row r="796">
-      <c r="A796" s="7"/>
+      <c r="A796" s="5"/>
     </row>
     <row r="797">
-      <c r="A797" s="7"/>
+      <c r="A797" s="5"/>
     </row>
     <row r="798">
-      <c r="A798" s="7"/>
+      <c r="A798" s="5"/>
     </row>
     <row r="799">
-      <c r="A799" s="7"/>
+      <c r="A799" s="5"/>
     </row>
     <row r="800">
-      <c r="A800" s="7"/>
+      <c r="A800" s="5"/>
     </row>
     <row r="801">
-      <c r="A801" s="7"/>
+      <c r="A801" s="5"/>
     </row>
     <row r="802">
-      <c r="A802" s="7"/>
+      <c r="A802" s="5"/>
     </row>
     <row r="803">
-      <c r="A803" s="7"/>
+      <c r="A803" s="5"/>
     </row>
     <row r="804">
-      <c r="A804" s="7"/>
+      <c r="A804" s="5"/>
     </row>
     <row r="805">
-      <c r="A805" s="7"/>
+      <c r="A805" s="5"/>
     </row>
     <row r="806">
-      <c r="A806" s="7"/>
+      <c r="A806" s="5"/>
     </row>
     <row r="807">
-      <c r="A807" s="7"/>
+      <c r="A807" s="5"/>
     </row>
     <row r="808">
-      <c r="A808" s="7"/>
+      <c r="A808" s="5"/>
     </row>
     <row r="809">
-      <c r="A809" s="7"/>
+      <c r="A809" s="5"/>
     </row>
     <row r="810">
-      <c r="A810" s="7"/>
+      <c r="A810" s="5"/>
     </row>
     <row r="811">
-      <c r="A811" s="7"/>
+      <c r="A811" s="5"/>
     </row>
     <row r="812">
-      <c r="A812" s="7"/>
+      <c r="A812" s="5"/>
     </row>
     <row r="813">
-      <c r="A813" s="7"/>
+      <c r="A813" s="5"/>
     </row>
     <row r="814">
-      <c r="A814" s="7"/>
+      <c r="A814" s="5"/>
     </row>
     <row r="815">
-      <c r="A815" s="7"/>
+      <c r="A815" s="5"/>
     </row>
     <row r="816">
-      <c r="A816" s="7"/>
+      <c r="A816" s="5"/>
     </row>
     <row r="817">
-      <c r="A817" s="7"/>
+      <c r="A817" s="5"/>
     </row>
     <row r="818">
-      <c r="A818" s="7"/>
+      <c r="A818" s="5"/>
     </row>
     <row r="819">
-      <c r="A819" s="7"/>
+      <c r="A819" s="5"/>
     </row>
     <row r="820">
-      <c r="A820" s="7"/>
+      <c r="A820" s="5"/>
     </row>
     <row r="821">
-      <c r="A821" s="7"/>
+      <c r="A821" s="5"/>
     </row>
     <row r="822">
-      <c r="A822" s="7"/>
+      <c r="A822" s="5"/>
     </row>
     <row r="823">
-      <c r="A823" s="7"/>
+      <c r="A823" s="5"/>
     </row>
     <row r="824">
-      <c r="A824" s="7"/>
+      <c r="A824" s="5"/>
     </row>
     <row r="825">
-      <c r="A825" s="7"/>
+      <c r="A825" s="5"/>
     </row>
     <row r="826">
-      <c r="A826" s="7"/>
+      <c r="A826" s="5"/>
     </row>
     <row r="827">
-      <c r="A827" s="7"/>
+      <c r="A827" s="5"/>
     </row>
     <row r="828">
-      <c r="A828" s="7"/>
+      <c r="A828" s="5"/>
     </row>
     <row r="829">
-      <c r="A829" s="7"/>
+      <c r="A829" s="5"/>
     </row>
     <row r="830">
-      <c r="A830" s="7"/>
+      <c r="A830" s="5"/>
     </row>
     <row r="831">
-      <c r="A831" s="7"/>
+      <c r="A831" s="5"/>
     </row>
     <row r="832">
-      <c r="A832" s="7"/>
+      <c r="A832" s="5"/>
     </row>
     <row r="833">
-      <c r="A833" s="7"/>
+      <c r="A833" s="5"/>
     </row>
     <row r="834">
-      <c r="A834" s="7"/>
+      <c r="A834" s="5"/>
     </row>
     <row r="835">
-      <c r="A835" s="7"/>
+      <c r="A835" s="5"/>
     </row>
     <row r="836">
-      <c r="A836" s="7"/>
+      <c r="A836" s="5"/>
     </row>
     <row r="837">
-      <c r="A837" s="7"/>
+      <c r="A837" s="5"/>
     </row>
     <row r="838">
-      <c r="A838" s="7"/>
+      <c r="A838" s="5"/>
     </row>
     <row r="839">
-      <c r="A839" s="7"/>
+      <c r="A839" s="5"/>
     </row>
     <row r="840">
-      <c r="A840" s="7"/>
+      <c r="A840" s="5"/>
     </row>
     <row r="841">
-      <c r="A841" s="7"/>
+      <c r="A841" s="5"/>
     </row>
     <row r="842">
-      <c r="A842" s="7"/>
+      <c r="A842" s="5"/>
     </row>
     <row r="843">
-      <c r="A843" s="7"/>
+      <c r="A843" s="5"/>
     </row>
     <row r="844">
-      <c r="A844" s="7"/>
+      <c r="A844" s="5"/>
     </row>
     <row r="845">
-      <c r="A845" s="7"/>
+      <c r="A845" s="5"/>
     </row>
     <row r="846">
-      <c r="A846" s="7"/>
+      <c r="A846" s="5"/>
     </row>
     <row r="847">
-      <c r="A847" s="7"/>
+      <c r="A847" s="5"/>
     </row>
     <row r="848">
-      <c r="A848" s="7"/>
+      <c r="A848" s="5"/>
     </row>
     <row r="849">
-      <c r="A849" s="7"/>
+      <c r="A849" s="5"/>
     </row>
     <row r="850">
-      <c r="A850" s="7"/>
+      <c r="A850" s="5"/>
     </row>
     <row r="851">
-      <c r="A851" s="7"/>
+      <c r="A851" s="5"/>
     </row>
     <row r="852">
-      <c r="A852" s="7"/>
+      <c r="A852" s="5"/>
     </row>
     <row r="853">
-      <c r="A853" s="7"/>
+      <c r="A853" s="5"/>
     </row>
     <row r="854">
-      <c r="A854" s="7"/>
+      <c r="A854" s="5"/>
     </row>
     <row r="855">
-      <c r="A855" s="7"/>
+      <c r="A855" s="5"/>
     </row>
     <row r="856">
-      <c r="A856" s="7"/>
+      <c r="A856" s="5"/>
     </row>
     <row r="857">
-      <c r="A857" s="7"/>
+      <c r="A857" s="5"/>
     </row>
     <row r="858">
-      <c r="A858" s="7"/>
+      <c r="A858" s="5"/>
     </row>
     <row r="859">
-      <c r="A859" s="7"/>
+      <c r="A859" s="5"/>
     </row>
     <row r="860">
-      <c r="A860" s="7"/>
+      <c r="A860" s="5"/>
     </row>
     <row r="861">
-      <c r="A861" s="7"/>
+      <c r="A861" s="5"/>
     </row>
     <row r="862">
-      <c r="A862" s="7"/>
+      <c r="A862" s="5"/>
     </row>
     <row r="863">
-      <c r="A863" s="7"/>
+      <c r="A863" s="5"/>
     </row>
     <row r="864">
-      <c r="A864" s="7"/>
+      <c r="A864" s="5"/>
     </row>
     <row r="865">
-      <c r="A865" s="7"/>
+      <c r="A865" s="5"/>
     </row>
     <row r="866">
-      <c r="A866" s="7"/>
+      <c r="A866" s="5"/>
     </row>
     <row r="867">
-      <c r="A867" s="7"/>
+      <c r="A867" s="5"/>
     </row>
     <row r="868">
-      <c r="A868" s="7"/>
+      <c r="A868" s="5"/>
     </row>
     <row r="869">
-      <c r="A869" s="7"/>
+      <c r="A869" s="5"/>
     </row>
     <row r="870">
-      <c r="A870" s="7"/>
+      <c r="A870" s="5"/>
     </row>
     <row r="871">
-      <c r="A871" s="7"/>
+      <c r="A871" s="5"/>
     </row>
     <row r="872">
-      <c r="A872" s="7"/>
+      <c r="A872" s="5"/>
     </row>
     <row r="873">
-      <c r="A873" s="7"/>
+      <c r="A873" s="5"/>
     </row>
     <row r="874">
-      <c r="A874" s="7"/>
+      <c r="A874" s="5"/>
     </row>
     <row r="875">
-      <c r="A875" s="7"/>
+      <c r="A875" s="5"/>
     </row>
     <row r="876">
-      <c r="A876" s="7"/>
+      <c r="A876" s="5"/>
     </row>
     <row r="877">
-      <c r="A877" s="7"/>
+      <c r="A877" s="5"/>
     </row>
     <row r="878">
-      <c r="A878" s="7"/>
+      <c r="A878" s="5"/>
     </row>
     <row r="879">
-      <c r="A879" s="7"/>
+      <c r="A879" s="5"/>
     </row>
     <row r="880">
-      <c r="A880" s="7"/>
+      <c r="A880" s="5"/>
     </row>
     <row r="881">
-      <c r="A881" s="7"/>
+      <c r="A881" s="5"/>
     </row>
     <row r="882">
-      <c r="A882" s="7"/>
+      <c r="A882" s="5"/>
     </row>
     <row r="883">
-      <c r="A883" s="7"/>
+      <c r="A883" s="5"/>
     </row>
     <row r="884">
-      <c r="A884" s="7"/>
+      <c r="A884" s="5"/>
     </row>
     <row r="885">
-      <c r="A885" s="7"/>
+      <c r="A885" s="5"/>
     </row>
     <row r="886">
-      <c r="A886" s="7"/>
+      <c r="A886" s="5"/>
     </row>
     <row r="887">
-      <c r="A887" s="7"/>
+      <c r="A887" s="5"/>
     </row>
     <row r="888">
-      <c r="A888" s="7"/>
+      <c r="A888" s="5"/>
     </row>
     <row r="889">
-      <c r="A889" s="7"/>
+      <c r="A889" s="5"/>
     </row>
     <row r="890">
-      <c r="A890" s="7"/>
+      <c r="A890" s="5"/>
     </row>
     <row r="891">
-      <c r="A891" s="7"/>
+      <c r="A891" s="5"/>
     </row>
     <row r="892">
-      <c r="A892" s="7"/>
+      <c r="A892" s="5"/>
     </row>
     <row r="893">
-      <c r="A893" s="7"/>
+      <c r="A893" s="5"/>
     </row>
     <row r="894">
-      <c r="A894" s="7"/>
+      <c r="A894" s="5"/>
     </row>
     <row r="895">
-      <c r="A895" s="7"/>
+      <c r="A895" s="5"/>
     </row>
     <row r="896">
-      <c r="A896" s="7"/>
+      <c r="A896" s="5"/>
     </row>
     <row r="897">
-      <c r="A897" s="7"/>
+      <c r="A897" s="5"/>
     </row>
     <row r="898">
-      <c r="A898" s="7"/>
+      <c r="A898" s="5"/>
     </row>
     <row r="899">
-      <c r="A899" s="7"/>
+      <c r="A899" s="5"/>
     </row>
     <row r="900">
-      <c r="A900" s="7"/>
+      <c r="A900" s="5"/>
     </row>
     <row r="901">
-      <c r="A901" s="7"/>
+      <c r="A901" s="5"/>
     </row>
     <row r="902">
-      <c r="A902" s="7"/>
+      <c r="A902" s="5"/>
     </row>
     <row r="903">
-      <c r="A903" s="7"/>
+      <c r="A903" s="5"/>
     </row>
     <row r="904">
-      <c r="A904" s="7"/>
+      <c r="A904" s="5"/>
     </row>
     <row r="905">
-      <c r="A905" s="7"/>
+      <c r="A905" s="5"/>
     </row>
     <row r="906">
-      <c r="A906" s="7"/>
+      <c r="A906" s="5"/>
     </row>
     <row r="907">
-      <c r="A907" s="7"/>
+      <c r="A907" s="5"/>
     </row>
     <row r="908">
-      <c r="A908" s="7"/>
+      <c r="A908" s="5"/>
     </row>
     <row r="909">
-      <c r="A909" s="7"/>
+      <c r="A909" s="5"/>
     </row>
     <row r="910">
-      <c r="A910" s="7"/>
+      <c r="A910" s="5"/>
     </row>
     <row r="911">
-      <c r="A911" s="7"/>
+      <c r="A911" s="5"/>
     </row>
     <row r="912">
-      <c r="A912" s="7"/>
+      <c r="A912" s="5"/>
     </row>
     <row r="913">
-      <c r="A913" s="7"/>
+      <c r="A913" s="5"/>
     </row>
     <row r="914">
-      <c r="A914" s="7"/>
+      <c r="A914" s="5"/>
     </row>
     <row r="915">
-      <c r="A915" s="7"/>
+      <c r="A915" s="5"/>
     </row>
     <row r="916">
-      <c r="A916" s="7"/>
+      <c r="A916" s="5"/>
     </row>
     <row r="917">
-      <c r="A917" s="7"/>
+      <c r="A917" s="5"/>
     </row>
     <row r="918">
-      <c r="A918" s="7"/>
+      <c r="A918" s="5"/>
     </row>
     <row r="919">
-      <c r="A919" s="7"/>
+      <c r="A919" s="5"/>
     </row>
     <row r="920">
-      <c r="A920" s="7"/>
+      <c r="A920" s="5"/>
     </row>
     <row r="921">
-      <c r="A921" s="7"/>
+      <c r="A921" s="5"/>
     </row>
     <row r="922">
-      <c r="A922" s="7"/>
+      <c r="A922" s="5"/>
     </row>
     <row r="923">
-      <c r="A923" s="7"/>
+      <c r="A923" s="5"/>
     </row>
     <row r="924">
-      <c r="A924" s="7"/>
+      <c r="A924" s="5"/>
     </row>
     <row r="925">
-      <c r="A925" s="7"/>
+      <c r="A925" s="5"/>
     </row>
     <row r="926">
-      <c r="A926" s="7"/>
+      <c r="A926" s="5"/>
     </row>
     <row r="927">
-      <c r="A927" s="7"/>
+      <c r="A927" s="5"/>
     </row>
     <row r="928">
-      <c r="A928" s="7"/>
+      <c r="A928" s="5"/>
     </row>
     <row r="929">
-      <c r="A929" s="7"/>
+      <c r="A929" s="5"/>
     </row>
     <row r="930">
-      <c r="A930" s="7"/>
+      <c r="A930" s="5"/>
     </row>
     <row r="931">
-      <c r="A931" s="7"/>
+      <c r="A931" s="5"/>
     </row>
     <row r="932">
-      <c r="A932" s="7"/>
+      <c r="A932" s="5"/>
     </row>
     <row r="933">
-      <c r="A933" s="7"/>
+      <c r="A933" s="5"/>
     </row>
     <row r="934">
-      <c r="A934" s="7"/>
+      <c r="A934" s="5"/>
     </row>
     <row r="935">
-      <c r="A935" s="7"/>
+      <c r="A935" s="5"/>
     </row>
     <row r="936">
-      <c r="A936" s="7"/>
+      <c r="A936" s="5"/>
     </row>
     <row r="937">
-      <c r="A937" s="7"/>
+      <c r="A937" s="5"/>
     </row>
     <row r="938">
-      <c r="A938" s="7"/>
+      <c r="A938" s="5"/>
     </row>
     <row r="939">
-      <c r="A939" s="7"/>
+      <c r="A939" s="5"/>
     </row>
     <row r="940">
-      <c r="A940" s="7"/>
+      <c r="A940" s="5"/>
     </row>
     <row r="941">
-      <c r="A941" s="7"/>
+      <c r="A941" s="5"/>
     </row>
     <row r="942">
-      <c r="A942" s="7"/>
+      <c r="A942" s="5"/>
     </row>
     <row r="943">
-      <c r="A943" s="7"/>
+      <c r="A943" s="5"/>
     </row>
     <row r="944">
-      <c r="A944" s="7"/>
+      <c r="A944" s="5"/>
     </row>
     <row r="945">
-      <c r="A945" s="7"/>
+      <c r="A945" s="5"/>
     </row>
     <row r="946">
-      <c r="A946" s="7"/>
+      <c r="A946" s="5"/>
     </row>
     <row r="947">
-      <c r="A947" s="7"/>
+      <c r="A947" s="5"/>
     </row>
     <row r="948">
-      <c r="A948" s="7"/>
+      <c r="A948" s="5"/>
     </row>
     <row r="949">
-      <c r="A949" s="7"/>
+      <c r="A949" s="5"/>
     </row>
     <row r="950">
-      <c r="A950" s="7"/>
+      <c r="A950" s="5"/>
     </row>
     <row r="951">
-      <c r="A951" s="7"/>
+      <c r="A951" s="5"/>
     </row>
     <row r="952">
-      <c r="A952" s="7"/>
+      <c r="A952" s="5"/>
     </row>
     <row r="953">
-      <c r="A953" s="7"/>
+      <c r="A953" s="5"/>
     </row>
     <row r="954">
-      <c r="A954" s="7"/>
+      <c r="A954" s="5"/>
     </row>
     <row r="955">
-      <c r="A955" s="7"/>
+      <c r="A955" s="5"/>
     </row>
     <row r="956">
-      <c r="A956" s="7"/>
+      <c r="A956" s="5"/>
     </row>
     <row r="957">
-      <c r="A957" s="7"/>
+      <c r="A957" s="5"/>
     </row>
     <row r="958">
-      <c r="A958" s="7"/>
+      <c r="A958" s="5"/>
     </row>
     <row r="959">
-      <c r="A959" s="7"/>
+      <c r="A959" s="5"/>
     </row>
     <row r="960">
-      <c r="A960" s="7"/>
+      <c r="A960" s="5"/>
     </row>
     <row r="961">
-      <c r="A961" s="7"/>
+      <c r="A961" s="5"/>
     </row>
     <row r="962">
-      <c r="A962" s="7"/>
+      <c r="A962" s="5"/>
     </row>
     <row r="963">
-      <c r="A963" s="7"/>
+      <c r="A963" s="5"/>
     </row>
     <row r="964">
-      <c r="A964" s="7"/>
+      <c r="A964" s="5"/>
     </row>
     <row r="965">
-      <c r="A965" s="7"/>
+      <c r="A965" s="5"/>
     </row>
     <row r="966">
-      <c r="A966" s="7"/>
+      <c r="A966" s="5"/>
     </row>
     <row r="967">
-      <c r="A967" s="7"/>
+      <c r="A967" s="5"/>
     </row>
     <row r="968">
-      <c r="A968" s="7"/>
+      <c r="A968" s="5"/>
     </row>
     <row r="969">
-      <c r="A969" s="7"/>
+      <c r="A969" s="5"/>
     </row>
     <row r="970">
-      <c r="A970" s="7"/>
+      <c r="A970" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
